--- a/docs/Revue-claude/Revue_exhaustive_des_remarques_Claude.xlsx
+++ b/docs/Revue-claude/Revue_exhaustive_des_remarques_Claude.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5a27edfabd428da/Documents/08. Administration Privée/Projet Application Routines/01. Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="11_21FE621596D0F2E6B5E8186B4460CD06EF1A1846" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{193E3CF3-2B4D-4FB6-8804-7F690293B8DB}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="11_21FE621596D0F2E6B5E8186B4460CD06EF1A1846" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9F7DD5E-16E6-4CC5-858A-27645AC6685A}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="25440" windowHeight="15257" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="1017">
   <si>
     <t>Nombre de Référence Claude</t>
   </si>
@@ -321,9 +321,6 @@
     <t>Le produit est local-first dans le MVP, mais le moteur et le schéma de stockage ne sont pas choisis. Ce choix doit aussi préparer la synchronisation future.</t>
   </si>
   <si>
-    <t>Résolu. Le chapitre 12 fixe désormais le stockage local du MVP : SQLite via expo-sqlite, avec Drizzle ORM sous réserve de validation de compatibilité stable. L’accès passe par des Repositories afin de préserver les migrations et une future synchronisation.</t>
-  </si>
-  <si>
     <t>Le chapitre 12 désormais complété fournit la décision technique nécessaire ; le point peut être clôturé sans nouvel arbitrage.</t>
   </si>
   <si>
@@ -357,9 +354,6 @@
     <t>La documentation ne précisait pas à partir de quand une séance en pause devait être interrompue plutôt que simplement reprise.</t>
   </si>
   <si>
-    <t>Résolu. La règle de reprise tardive est documentée : après 30 minutes en pause, l’utilisateur doit choisir de reprendre ou d’arrêter ; sans réponse, l’Exécution est automatiquement enregistrée comme Interrompue. La documentation a été harmonisée sans délai supplémentaire non validé.</t>
-  </si>
-  <si>
     <t>Audit transversal effectué. La règle des 30 minutes est cohérente dans les chapitres concernés ; le libellé résiduel « terminer » a été harmonisé en « arrêter ».</t>
   </si>
   <si>
@@ -564,9 +558,6 @@
     <t>Claude demandait de confirmer son maintien ou sa suppression.</t>
   </si>
   <si>
-    <t>Résolu. Le bouton Précédent est exclu du MVP. Pendant l’Exécution, l’utilisateur peut passer à l’Activité suivante selon les règles de confirmation définies, mais ne peut pas choisir arbitrairement une étape antérieure.</t>
-  </si>
-  <si>
     <t>3.9</t>
   </si>
   <si>
@@ -594,9 +585,6 @@
     <t>Claude recommande de choisir un stockage local compatible avec migrations et synchronisation future.</t>
   </si>
   <si>
-    <t>Résolu. Le moteur de stockage local est défini dans le chapitre 12 : SQLite via expo-sqlite, Drizzle ORM sous réserve de compatibilité stable, migrations et couche Repository.</t>
-  </si>
-  <si>
     <t>3.11</t>
   </si>
   <si>
@@ -612,9 +600,6 @@
     <t>Claude propose notamment Zustand ou Jotai, une couche repository, Jest/RNTL et Maestro ou Detox.</t>
   </si>
   <si>
-    <t>Résolu. Le chapitre 12 définit la gestion d’état et les tests : SQLite pour l’état persistant, React state/reducer/Context pour l’état UI temporaire, moteur TypeScript indépendant de React, Jest/jest-expo/RNTL et Maestro pour les parcours E2E stabilisés.</t>
-  </si>
-  <si>
     <t>3.12</t>
   </si>
   <si>
@@ -639,9 +624,6 @@
     <t>Claude demandait le délai et le comportement après une longue suspension.</t>
   </si>
   <si>
-    <t>Résolu. La règle de reprise tardive est fixée à 30 minutes de pause, avec reprise explicite ou interruption ; sans réponse, l’Exécution est enregistrée comme Interrompue.</t>
-  </si>
-  <si>
     <t>3.14</t>
   </si>
   <si>
@@ -654,9 +636,6 @@
     <t>Claude recommande que le glossaire devienne la référence unique pour les types et noms du code.</t>
   </si>
   <si>
-    <t>Résolu. Le glossaire a été consolidé et déclaré référence terminologique fonctionnelle du projet. Les noms techniques du code doivent rester explicitement rattachables aux concepts du glossaire et ne pas introduire de concept métier concurrent.</t>
-  </si>
-  <si>
     <t>4.1</t>
   </si>
   <si>
@@ -675,9 +654,6 @@
     <t>Architecture local-first, cœur métier TypeScript pur, indépendant de React Native et ports substituables.</t>
   </si>
   <si>
-    <t>Validé et documenté. L’architecture du MVP est local-first, structurée en couches, avec domaine métier indépendant de l’UI et de la plateforme, services applicatifs, Repositories et stockage local.</t>
-  </si>
-  <si>
     <t>4.2</t>
   </si>
   <si>
@@ -696,9 +672,6 @@
     <t>Moteur d’exécution pur sans dépendance native.</t>
   </si>
   <si>
-    <t>Validé et documenté. Le moteur d’Exécution est un module TypeScript indépendant de React et des APIs natives. Les capacités de plateforme sont accessibles via des adaptateurs dédiés.</t>
-  </si>
-  <si>
     <t>4.4</t>
   </si>
   <si>
@@ -708,9 +681,6 @@
     <t>Interfaces de repository et implémentation locale remplaçable.</t>
   </si>
   <si>
-    <t>Validé et documenté. L’accès aux données passe par des Repositories afin de découpler les services métier de SQLite/Drizzle et de préparer une éventuelle source distante future.</t>
-  </si>
-  <si>
     <t>4.5</t>
   </si>
   <si>
@@ -720,9 +690,6 @@
     <t>Identifiants stables générés côté client.</t>
   </si>
   <si>
-    <t>Validé et documenté. Les identifiants sont uniques et stables ; l’Utilisateur local reçoit au premier lancement un UUID ou équivalent, et les entités persistantes utilisent des identifiants stables.</t>
-  </si>
-  <si>
     <t>4.6</t>
   </si>
   <si>
@@ -735,9 +702,6 @@
     <t>Préparer partage et rôles futurs.</t>
   </si>
   <si>
-    <t>Résolu. Les racines d’agrégat persistantes appartenant à l’Utilisateur, notamment Séance, Routine, Exécution et Catégorie, portent un ownerId vers l’Utilisateur interne. Les objets enfants héritent de cette propriété par leur rattachement et ne dupliquent pas systématiquement ownerId.</t>
-  </si>
-  <si>
     <t>4.7</t>
   </si>
   <si>
@@ -750,9 +714,6 @@
     <t>Créer dès maintenant une interface pour une future IA.</t>
   </si>
   <si>
-    <t>Décision prise : aucun port IA vide/no-op n’est créé dans le MVP. Une interface IA ne sera introduite que lorsqu’un cas d’usage concret sera retenu, afin d’éviter une abstraction prématurée.</t>
-  </si>
-  <si>
     <t>4.8</t>
   </si>
   <si>
@@ -765,9 +726,6 @@
     <t>Isoler les services natifs derrière des interfaces.</t>
   </si>
   <si>
-    <t>Validé et documenté. Les fonctions natives Audio, voix, vibrations, notifications, médias et horloge sont isolées derrière des adaptateurs/interfaces techniques dédiés.</t>
-  </si>
-  <si>
     <t>4.9</t>
   </si>
   <si>
@@ -780,9 +738,6 @@
     <t>Empêcher le domaine d’importer React Native et préserver react-native-web.</t>
   </si>
   <si>
-    <t>Validé. Le Web est hors MVP, mais le domaine et les services ne doivent pas dépendre directement de React Native. L’architecture évite donc de bloquer artificiellement une évolution Web future.</t>
-  </si>
-  <si>
     <t>4.10</t>
   </si>
   <si>
@@ -795,9 +750,6 @@
     <t>Gestion d’état UI et cache.</t>
   </si>
   <si>
-    <t>Décision prise. Zustand n’est pas introduit au démarrage. L’état persistant est dans SQLite ; l’état UI temporaire utilise React state/reducer/Context. Une bibliothèque globale ne sera ajoutée qu’en présence d’un besoin réel.</t>
-  </si>
-  <si>
     <t>4.11</t>
   </si>
   <si>
@@ -807,9 +759,6 @@
     <t>Stratégie de tests unitaires, composants et e2e.</t>
   </si>
   <si>
-    <t>Validé et documenté. La stratégie de tests retient Jest + jest-expo + React Native Testing Library, des tests unitaires renforcés du domaine et du moteur, puis Maestro pour les parcours end-to-end stabilisés.</t>
-  </si>
-  <si>
     <t>4.12</t>
   </si>
   <si>
@@ -837,9 +786,6 @@
     <t>Squelette Expo Router, thème, stockage, tests et compilation iOS/Android/Web.</t>
   </si>
   <si>
-    <t>Proposition acceptée sous la forme définie par le chapitre 12. Le socle technique est React Native + Expo, TypeScript strict, Expo Router, SQLite/expo-sqlite, tests automatisés et builds Expo EAS pour iOS/Android.</t>
-  </si>
-  <si>
     <t>5.1</t>
   </si>
   <si>
@@ -849,9 +795,6 @@
     <t>Claude utilise « routine » pour le contenu créé dans Mes routines.</t>
   </si>
   <si>
-    <t>Proposition corrigée. La phase doit créer une Séance, et non une Routine. Une Routine est exclusivement la planification d’une Séance dans le Calendrier.</t>
-  </si>
-  <si>
     <t>5.2</t>
   </si>
   <si>
@@ -870,9 +813,6 @@
     <t>Créer Pause comme type autonome.</t>
   </si>
   <si>
-    <t>Proposition corrigée. Le type métier autonome est Récupération. Une Pause après activité est saisie comme paramètre d’un Exercice et matérialisée dans le modèle par une Récupération associée, masquée comme objet autonome dans la composition.</t>
-  </si>
-  <si>
     <t>5.4</t>
   </si>
   <si>
@@ -882,9 +822,6 @@
     <t>Déplacer, dupliquer, supprimer et annuler.</t>
   </si>
   <si>
-    <t>Proposition conforme aux règles fonctionnelles actuelles. La réorganisation, la duplication et la suppression des éléments sont conservées selon les comportements et confirmations définis dans la documentation.</t>
-  </si>
-  <si>
     <t>5.5</t>
   </si>
   <si>
@@ -894,9 +831,6 @@
     <t>Claude conserve l’ancienne terminologie Série.</t>
   </si>
   <si>
-    <t>Proposition corrigée terminologiquement. Utiliser Bloc et Cycle ; « Série » n’est pas une entité métier. Dans le MVP, une Séance contient un Cycle unique et le Cycle contient un Bloc unique, chacun avec son nombre de répétitions.</t>
-  </si>
-  <si>
     <t>5.6</t>
   </si>
   <si>
@@ -906,9 +840,6 @@
     <t>Claude traite les deux comme objets comparables.</t>
   </si>
   <si>
-    <t>Proposition corrigée. Le Compte à rebours initial est une étape d’Exécution ; la Fin de Séance est un élément structurel distinct exécuté après la dernière Activité et ne constitue pas une Activité.</t>
-  </si>
-  <si>
     <t>5.7</t>
   </si>
   <si>
@@ -918,9 +849,6 @@
     <t>Durée estimée et blocage si séance invalide.</t>
   </si>
   <si>
-    <t>Proposition conforme. La validation doit empêcher l’exécution d’une Séance invalide et le résumé doit présenter les informations nécessaires, notamment la durée estimée selon les règles définies.</t>
-  </si>
-  <si>
     <t>5.8</t>
   </si>
   <si>
@@ -930,9 +858,6 @@
     <t>Construire le plan depuis un instantané et le tester sans UI.</t>
   </si>
   <si>
-    <t>Proposition validée. Le moteur d’Exécution est explicitement défini dans le chapitre 12 comme un module TypeScript pur, indépendant de React, testable sans interface et construit à partir de l’Instantané.</t>
-  </si>
-  <si>
     <t>5.9</t>
   </si>
   <si>
@@ -942,9 +867,6 @@
     <t>Preuve bout-en-bout avant toutes les variantes.</t>
   </si>
   <si>
-    <t>Proposition validée comme stratégie de réduction du risque. Une première preuve bout-en-bout chronométrée peut être réalisée avant les variantes, tout en conservant le moteur et les commandes cibles définis dans l’architecture.</t>
-  </si>
-  <si>
     <t>5.10</t>
   </si>
   <si>
@@ -954,9 +876,6 @@
     <t>Ajouter progressivement les répétitions et modes manuels.</t>
   </si>
   <si>
-    <t>Proposition conforme après correction de terminologie. Les répétitions du Bloc et du Cycle et les modes d’Activité sont intégrés progressivement sur le moteur d’Exécution défini.</t>
-  </si>
-  <si>
     <t>5.11</t>
   </si>
   <si>
@@ -978,9 +897,6 @@
     <t>Développer les cas d’interruption.</t>
   </si>
   <si>
-    <t>Proposition conforme. Les commandes MVP sont Réinitialiser, Pause/Reprendre et Activité suivante ; Réinitialiser et Activité suivante demandent confirmation, et l’arrêt est accessible uniquement depuis l’état Pause.</t>
-  </si>
-  <si>
     <t>5.13</t>
   </si>
   <si>
@@ -990,9 +906,6 @@
     <t>Créer d’abord l’historique et la synthèse minimale.</t>
   </si>
   <si>
-    <t>Proposition conforme. L’historique et la synthèse peuvent être construits avant les champs facultatifs de ressenti, à condition de conserver l’Instantané et les statuts d’Exécution définis.</t>
-  </si>
-  <si>
     <t>5.14</t>
   </si>
   <si>
@@ -1002,9 +915,6 @@
     <t>Inclure douleur/gêne dans la phase MVP.</t>
   </si>
   <si>
-    <t>Proposition corrigée. Le ressenti général et la note libre font partie du MVP. Le signalement douleur/gêne est hors MVP et prévu pour une version ultérieure. La documentation V1 a été harmonisée sur ce périmètre.</t>
-  </si>
-  <si>
     <t>5.15</t>
   </si>
   <si>
@@ -1014,9 +924,6 @@
     <t>Liste chronologique sous réserve d’arbitrage.</t>
   </si>
   <si>
-    <t>Proposition corrigée selon l’arbitrage déjà réalisé. Le Suivi MVP n’est pas une simple liste : il comprend recherche, filtres, tri et affichage condensé/déployé des Exécutions.</t>
-  </si>
-  <si>
     <t>5.16</t>
   </si>
   <si>
@@ -1026,9 +933,6 @@
     <t>Créer un écran de détail d’exécution.</t>
   </si>
   <si>
-    <t>Proposition corrigée. Aucun écran de détail séparé n’est prévu dans le MVP ; le détail d’une Exécution est consulté directement par déploiement de sa carte dans le Suivi.</t>
-  </si>
-  <si>
     <t>5.17</t>
   </si>
   <si>
@@ -1038,9 +942,6 @@
     <t>CRUD et association multiple.</t>
   </si>
   <si>
-    <t>Proposition précisée. Les Catégories sont personnalisables : création, modification et suppression. Si une Catégorie utilisée est supprimée, elle est retirée des Séances concernées après confirmation ; les Instantanés historiques restent inchangés.</t>
-  </si>
-  <si>
     <t>5.18</t>
   </si>
   <si>
@@ -1050,9 +951,6 @@
     <t>CRUD et association aux exercices.</t>
   </si>
   <si>
-    <t>Proposition corrigée. Les Zones corporelles ne disposent d’aucun CRUD utilisateur dans le MVP. Elles constituent un référentiel applicatif prédéfini que l’utilisateur peut uniquement consulter et sélectionner pour les Activités de type Exercice.</t>
-  </si>
-  <si>
     <t>5.19</t>
   </si>
   <si>
@@ -1071,9 +969,6 @@
     <t>Claude parle de routines pour le catalogue.</t>
   </si>
   <si>
-    <t>Proposition corrigée. Duplication, archivage et suppression concernent les Séances du catalogue. Les Routines sont des planifications : elles peuvent être créées, modifiées ou supprimées, mais n’ont plus d’état actif/inactif. Archiver une Séance supprime ses Routines ; restaurer la Séance ne les restaure pas.</t>
-  </si>
-  <si>
     <t>Audit transversal effectué. Le modal d’options contenait encore « Restaurer si la routine est archivée » ; corrigé en « séance archivée », conformément au modèle Séance/Routine.</t>
   </si>
   <si>
@@ -2577,155 +2472,36 @@
     <t>Étiquettes de lignes</t>
   </si>
   <si>
-    <t>Le MVP est monolingue en français et ne comporte aucun sélecteur de langue. L’architecture est préparée pour une évolution multilingue simple : textes externalisés dans un catalogue de ressources, ajout futur de langues sans refonte et gestion future distincte de la langue de l’interface et de la synthèse vocale.</t>
-  </si>
-  <si>
     <t>Décision produit validée : français uniquement dans le MVP, sans sélecteur, avec architecture préparée pour le multilingue.</t>
   </si>
   <si>
-    <t>Les textes de l’interface sont externalisés dès le MVP et ne sont pas codés en dur dans les composants. Le changement de langue n’est pas exposé dans le MVP mais pourra être ajouté ultérieurement, y compris pour la langue des annonces vocales.</t>
-  </si>
-  <si>
     <t>Même arbitrage que 2.17 ; préparation technique sans ajouter de fonction multilingue au MVP.</t>
   </si>
   <si>
     <t>Organisation validée pour faciliter maintenance, tests et développement assisté par IA sans disperser la logique métier.</t>
   </si>
   <si>
-    <t>Le MVP intègre dès le socle accessibilité de base, responsive mobile et design tokens centralisés. Il cible les principales tailles d’écran iOS/Android et un agrandissement raisonnable du texte. Il est conçu et testé en portrait, tout en préparant l’ajout ultérieur du paysage. Tablette dédiée et dark mode sont hors MVP.</t>
-  </si>
-  <si>
     <t>Niveau d’exigence MVP validé sans développer prématurément tablette, paysage ou dark mode.</t>
   </si>
   <si>
-    <t>La construction est volontairement incrémentale : une Séance simple avec quelques Activités est développée avant l’introduction complète de la mécanique Bloc/Cycle. Cette simplification est temporaire et ne modifie ni le modèle cible ni le périmètre du MVP.</t>
-  </si>
-  <si>
     <t>Stratégie validée pour réduire le risque et obtenir rapidement un premier parcours fonctionnel testable.</t>
   </si>
   <si>
-    <t>Le Profil du MVP ne comporte aucun sélecteur de langue. Les Préférences conservent les réglages MVP utiles ; l’architecture prépare l’ajout futur de la langue de l’interface et de la voix sans exposer ces choix dans le MVP.</t>
-  </si>
-  <si>
     <t>Le périmètre Profil/Préférences est cohérent avec la décision de MVP monolingue.</t>
   </si>
   <si>
-    <t>Les règles essentielles d’accessibilité et de responsive sont appliquées dès les composants du MVP et contrôlées avant livraison. Le design system utilise des tokens centralisés. Un seul layout est développé ; l’architecture permet une refonte ultérieure ou des variantes de présentation sans toucher au domaine métier.</t>
-  </si>
-  <si>
     <t>Traitement regroupé avec 4.12 afin d’éviter une correction massive de l’interface en fin de développement.</t>
   </si>
   <si>
-    <t>L’ordre retenu est : socle technique ; spike critique timer/audio/arrière-plan ; Séance simple ; premier moteur d’Exécution bout-en-bout ; structure complète ; Exécution complète ; Historique/Suivi ; Planification/Agenda/notifications ; Catégories/Zones/Profil/Préférences ; robustesse, accessibilité, responsive, E2E et stabilisation. Figma reste la référence UI cible.</t>
-  </si>
-  <si>
     <t>Cet ordre fait remonter le principal risque technique très tôt et impose qu’une étape soit fonctionnelle et testée avant la suivante.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Le code est organisé principalement par domaine fonctionnel. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>app/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> contient les routes et points d’entrée Expo Router ; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>src/features/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> regroupe les domaines, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>domain/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> les règles transverses, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>infrastructure/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> les capacités techniques, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>shared/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> les éléments communs et </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>e2e/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve"> les parcours de test. Les noms techniques sont en anglais et restent rattachables au glossaire français.</t>
-    </r>
-  </si>
-  <si>
     <t>Résolu. La suppression d’une Routine supprime uniquement cette planification et met fin au calcul de ses occurrences futures. Elle ne supprime jamais les Exécutions, Instantanés, résultats ni occurrences déjà historisées. Par ailleurs, l’archivage d’une Séance supprime les Routines qui lui sont associées ; la restauration ultérieure de la Séance ne recrée pas ces Routines. L’historique reste dans tous les cas conservé.</t>
   </si>
   <si>
     <t>Résolu. La « Pause après activité » est volontairement représentée différemment dans l’UX et dans le modèle. Pour l’utilisateur, il s’agit d’un paramètre facultatif d’une Activité de type Exercice. Dans le modèle, lorsqu’elle est renseignée, elle est matérialisée par une Activité autonome de type Récupération, liée à l’Exercice et exécutée immédiatement après lui. Cette Récupération n’est pas présentée comme une Activité autonome dans l’interface de composition. Il n’existe que deux types métier d’Activité : Exercice et Récupération ; « Pause » n’est pas un troisième type.</t>
   </si>
   <si>
-    <t>Résolu. Le glossaire a été complété et constitue désormais la référence terminologique fonctionnelle du projet. Les concepts Activité, Bloc, Cycle, Séance, Routine, Exécution, Récupération, etc. y sont définis conformément au modèle retenu. « Série » n’est plus une entité métier. Les noms techniques du code pourront être en anglais, mais devront rester explicitement rattachables aux concepts définis dans ce glossaire et ne pas introduire de vocabulaire métier concurrent.</t>
-  </si>
-  <si>
-    <t>Résolu. Le chapitre 11 – API fonctionnelles a été entièrement rédigé. Il ne duplique plus le modèle de données. Il définit les API internes correspondant aux opérations fonctionnelles du MVP, leurs responsabilités et leurs règles, ainsi que les principes retenus pour les contrats d’échange, formats, protocoles, découpage des services et gestion des erreurs. Les API externes futures — calendrier externe, contenus/médias tiers, etc. — restent hors MVP mais l’architecture permet leur ajout ultérieur.</t>
-  </si>
-  <si>
-    <t>Résolu. Le chapitre 12 – Architecture technique a été rédigé et les principaux choix d’architecture du MVP sont désormais validés : React Native + Expo, TypeScript strict, Expo Router, architecture local-first, SQLite via expo-sqlite, Drizzle ORM sous réserve de compatibilité stable, couche Repository, moteur d’Exécution TypeScript indépendant de React, isolation des capacités natives par adaptateurs, stratégie de tests Jest/jest-expo/React Native Testing Library puis Maestro, architecture préparée à l’i18n et à une synchronisation/cloud future. L’organisation du code par domaines fonctionnels, les design tokens, le responsive et les principes d’accessibilité sont également définis. Le principal point technique restant à valider expérimentalement concerne le comportement timer/audio/arrière-plan/écran verrouillé sur iOS et Android, traité séparément par le spike technique 2.15/3.12.</t>
-  </si>
-  <si>
     <t>Le risque est explicitement pris en compte. Le moteur d’Exécution ne reposera pas sur la continuité d’un timer JavaScript ni sur le comptage de ticks : il utilisera des horodatages de référence permettant de recalculer de manière déterministe l’état de l’Exécution et le temps restant après une suspension ou une reprise. Le moteur est indépendant de React et l’horloge est abstraite pour permettre les tests. Un spike technique obligatoire sur appareils iOS et Android réels sera réalisé avant le développement complet du moteur afin de valider le comportement en arrière-plan, écran verrouillé et reprise, notamment pour les transitions, sons et annonces vocales. Les résultats pourront adapter l’implémentation technique sans modifier le modèle fonctionnel.</t>
   </si>
   <si>
@@ -2741,13 +2517,7 @@
     <t>La stratégie et le périmètre du spike sont désormais définis, mais Claude demande ici un résultat expérimental. Le point ne peut donc être déclaré résolu avant exécution et documentation du spike.</t>
   </si>
   <si>
-    <t>Le moteur d’Exécution utilise un modèle temporel fondé sur des horodatages et un recalcul déterministe. Les timers utilisés par l’interface servent uniquement au rafraîchissement visuel et ne constituent jamais la source de vérité temporelle. Le moteur est indépendant de React et des APIs natives ; l’horloge, l’audio, la synthèse vocale et les autres capacités de plateforme sont accessibles par interfaces/adaptateurs. L’état nécessaire à la reconstruction d’une Exécution est persisté. Le choix définitif des mécanismes natifs nécessaires au fonctionnement en arrière-plan et écran verrouillé sera arrêté après le spike iOS/Android.</t>
-  </si>
-  <si>
     <t>Décision prise – validation par spike requise,</t>
-  </si>
-  <si>
-    <t>La validation sur appareils réels est intégrée au processus de développement. Les fonctions dépendantes du comportement de la plateforme — notamment timer, transitions, arrière-plan, verrouillage, suspension/reprise, audio, synthèse vocale, vibrations et notifications — doivent être testées sur au moins un appareil iOS réel et un appareil Android réel. Une première campagne est réalisée dans le cadre du spike technique avant le développement complet du moteur d’Exécution, puis une validation complète est effectuée avant livraison du MVP. Les simulateurs ne constituent pas à eux seuls une validation suffisante de ces comportements.</t>
   </si>
   <si>
     <t>Décision prise – validation sur appareils requise</t>
@@ -3616,12 +3386,84 @@
   <si>
     <t>Résolu. L’Agenda, la planification et les rappels locaux font partie du MVP. Une Routine associe une Séance à une planification qui peut être sans répétition ou hebdomadaire. Pour une répétition hebdomadaire, l’utilisateur définit une fréquence de N semaines (N ≥ 1), sélectionne un ou plusieurs jours de la semaine et renseigne une date de fin obligatoire. La sélection des sept jours permet de reproduire un comportement quotidien ; il n’existe donc pas de type « Quotidienne » distinct. Plusieurs planifications d’une même Séance à des horaires différents sont représentées par plusieurs Routines distinctes. Les récurrences mensuelles, annuelles et personnalisées sont exclues du MVP. Les Routines calculent les occurrences futures et les rappels reposent sur des notifications locales, sous réserve des autorisations iOS/Android.</t>
   </si>
+  <si>
+    <t>Résolu. Le bouton permettant de revenir à l’activité précédente pendant l’exécution a été supprimé du MVP. Une vérification transversale de la documentation de référence confirme qu’aucune occurrence résiduelle ne décrit encore cette fonctionnalité. Les occurrences du terme « précédent » restantes concernent d’autres notions (écran précédent, périodes précédentes, valeur précédente, etc.). Le chapitre 11 confirme explicitement qu’il n’existe aucun retour à une étape précédente pendant l’exécution.</t>
+  </si>
+  <si>
+    <t>Résolu. Le MVP est monolingue en français et ne comporte aucun sélecteur de langue. L’écran Profil et sa documentation ont été alignés en conséquence. L’architecture est néanmoins préparée dès le MVP à une évolution multilingue : les textes d’interface sont externalisés dans des ressources de traduction et référencés par des clés stables, sans être codés en dur dans les composants. L’ajout d’autres langues, la détection ou le choix de la langue et une éventuelle préférence utilisateur associée sont hors périmètre du MVP.</t>
+  </si>
+  <si>
+    <t>Résolu. Le stockage local du MVP repose sur SQLite via expo-sqlite, avec Drizzle ORM pour le schéma typé et les migrations sous réserve de compatibilité stable. L’accès aux données est encapsulé derrière une couche Repository. Cette architecture permet l’ajout ultérieur d’un stockage distant et d’un mécanisme de synchronisation pour les fonctions multi-appareils, partage, communauté et relation avec des professionnels, sans refonte du modèle métier. La technologie cloud n’est pas choisie à ce stade.</t>
+  </si>
+  <si>
+    <t>Résolu. Le MVP n’introduit pas Zustand au démarrage. Les données persistantes sont gérées dans SQLite via les Repositories ; l’état UI temporaire reste local aux composants et écrans React. Une librairie d’état global ne sera introduite que si un besoin transverse concret apparaît. La stratégie de tests retient Jest pour le domaine et le moteur d’Exécution, React Native Testing Library pour les composants et écrans, Maestro pour les parcours E2E critiques, complétés par des tests sur appareils réels pour les comportements natifs sensibles.</t>
+  </si>
+  <si>
+    <t>Décision prise – validation technique à réaliser</t>
+  </si>
+  <si>
+    <t>Résolu. La règle de reprise tardive est fixée à 30 minutes. Après 30 minutes en pause, l’utilisateur doit choisir de reprendre ou d’arrêter l’Exécution ; en l’absence de réponse, celle-ci est enregistrée comme Interrompue. Le statut Interrompue est désormais explicitement intégré au modèle de données, aux règles métier et aux écrans concernés. La règle est également enregistrée dans le registre des décisions.</t>
+  </si>
+  <si>
+    <t>Résolu. La règle de reprise tardive est fixée à 30 minutes et harmonisée transversalement dans la documentation. Le statut Interrompue est désormais pris en charge par le modèle de données et les règles métier, et la décision est formalisée dans le registre des décisions.</t>
+  </si>
+  <si>
+    <t>Résolu. Le glossaire constitue désormais la référence du vocabulaire métier et a été harmonisé avec les décisions de conception et le modèle fonctionnel. Les concepts structurants sont définis sans ambiguïté, notamment Séance, Routine, Cycle, Bloc, Activité, Exercice, Récupération et Série. Il couvre également les notions nécessaires à l’exécution et à l’historisation, notamment Utilisateur, Exécution, Plan d’exécution, Instantané de séance et les statuts d’exécution, dont Interrompue.</t>
+  </si>
+  <si>
+    <t>Résolu. Le glossaire a été complété et vérifié transversalement après stabilisation de la terminologie. Il est aligné avec la structure Séance → Cycle → Bloc → Activité et avec les concepts utilisés dans le modèle de données et l’Exécution. Les notions manquantes Utilisateur, Instantané de séance et Plan d’exécution ont été ajoutées, et le statut Interrompue a été intégré aux statuts d’exécution.</t>
+  </si>
+  <si>
+    <t>Résolu. Le chapitre 11 – API fonctionnelles a été rédigé puis vérifié transversalement avec la conception fonctionnelle, le modèle de données et les règles métier. Il couvre désormais les principales opérations fonctionnelles du MVP sans dupliquer le modèle de données. La revue finale a notamment permis d’intégrer explicitement la gestion des rappels locaux et de la suspension prolongée avec le statut Interrompue, et de retirer du MVP l’API relative aux indicateurs de suivi avancés. Les API fonctionnelles restent indépendantes de l’implémentation technique du stockage grâce à la couche Repository.</t>
+  </si>
+  <si>
+    <t>Résolu. Le chapitre 12 – Architecture technique a été entièrement rédigé et vérifié transversalement. Il définit l’architecture local-first, le découpage en couches, la persistance locale, les Repositories, l’identité utilisateur, la gestion d’état, le moteur d’Exécution, les capacités natives, les tests, les risques techniques, l’évolutivité, l’organisation du code et la stratégie de développement incrémental. Les principaux choix technologiques sont explicitement documentés et les points nécessitant encore une validation expérimentale sont isolés sous forme de spikes techniques.</t>
+  </si>
+  <si>
+    <t>Validé et documenté. L’architecture du MVP est local-first et organisée en couches séparant interface utilisateur, services applicatifs, domaine métier, Repositories et stockage local. Les fonctions du MVP restent utilisables hors connexion et aucun backend n’est requis.</t>
+  </si>
+  <si>
+    <t>Validé avec adaptation. Le code est organisé principalement par domaines fonctionnels. Expo Router porte les routes et points d’entrée des écrans ; la logique métier est regroupée par domaines dans src/features, les éléments partagés dans shared et les capacités techniques dans infrastructure. Aucun dossier global store/ n’est créé au démarrage puisque Zustand/Redux ne sont pas retenus pour le MVP.</t>
+  </si>
+  <si>
+    <t>Validé et documenté. Le domaine métier et le moteur d’Exécution sont indépendants de React Native et des APIs natives. Les règles métier, transitions et calculs sont implémentés en TypeScript testable indépendamment de l’interface, du stockage et de la plateforme.</t>
+  </si>
+  <si>
+    <t>Validé et documenté. L’accès aux données passe par une couche Repository. Les services applicatifs et le domaine ne dépendent pas directement de SQLite ou de Drizzle ORM, ce qui permet de faire évoluer le stockage ou d’ajouter ultérieurement une source distante et une synchronisation cloud sans refonte du domaine métier.</t>
+  </si>
+  <si>
+    <t>Validé et documenté. Les entités persistantes utilisent des identifiants uniques et stables générés côté client, de type UUID ou équivalent, afin de garantir la stabilité des références et de préparer une future synchronisation multi-appareils.</t>
+  </si>
+  <si>
+    <t>Validé avec précision de périmètre. Les principales racines d’agrégat appartenant à l’utilisateur — notamment Séance, Routine, Exécution et Catégorie — portent un ownerId vers l’Utilisateur interne. Les objets enfants comme Cycle, Bloc et Activité héritent de cette propriété par leur rattachement à l’agrégat et ne dupliquent pas systématiquement ownerId.</t>
+  </si>
+  <si>
+    <t>Validé et documenté. Les capacités natives nécessaires au guidage et au fonctionnement de l’application — audio, synthèse vocale, vibrations/haptique, notifications, fichiers/médias et horloge — sont isolées derrière des services ou adaptateurs dédiés afin que le domaine et le moteur d’Exécution ne dépendent pas directement des APIs iOS/Android.</t>
+  </si>
+  <si>
+    <t>Validé comme principe d’évolutivité. Le Web est hors périmètre du MVP, mais le domaine métier, les services applicatifs et les règles de gestion ne doivent pas dépendre inutilement de React Native ou d’APIs strictement mobiles. L’architecture doit permettre une évolution Web ultérieure sans refonte du cœur métier.</t>
+  </si>
+  <si>
+    <t>Décision prise. Zustand n’est pas introduit au démarrage du MVP. Les données persistantes sont gérées dans SQLite via les Repositories et l’état UI temporaire avec useState, useReducer et Context lorsque nécessaire. Une librairie globale d’état ne sera ajoutée que si un besoin transverse concret apparaît pendant le développement.</t>
+  </si>
+  <si>
+    <t>Validé et documenté. La stratégie de tests retient Jest + jest-expo pour le domaine et le moteur d’Exécution, React Native Testing Library pour les composants et écrans, Maestro pour les parcours end-to-end critiques après stabilisation, et des tests obligatoires sur appareils iOS et Android réels pour les comportements natifs sensibles.</t>
+  </si>
+  <si>
+    <t>Validé et documenté. Le MVP applique dès le socle des design tokens centralisés, les règles essentielles d’accessibilité et un responsive adapté aux principales tailles d’écran iOS/Android. Il est conçu et testé en portrait, tout en évitant les dimensions codées en dur afin de préparer une évolution ultérieure vers d’autres orientations ou layouts.</t>
+  </si>
+  <si>
+    <t>Référence</t>
+  </si>
+  <si>
+    <t>Validé avec adaptation. Le développement commence par un socle technique React Native / Expo avec Expo Router, TypeScript strict, SQLite, architecture en couches, tests, design tokens et préparation i18n. Le MVP cible iOS et Android ; le Web reste hors MVP mais l’architecture ne doit pas en bloquer une évolution future.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -3644,10 +3486,6 @@
       <b/>
       <sz val="8"/>
       <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3689,7 +3527,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3731,6 +3569,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4030,7 +3871,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Revue_exhaustive_des_remarques_Claude_20260818 - Copie.xlsx]PVT!Tableau croisé dynamique1</c:name>
+    <c:name>[Revue_exhaustive_des_remarques_Claude.xlsx]PVT!Tableau croisé dynamique1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -7383,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>842</v>
+        <v>807</v>
       </c>
       <c r="F1"/>
       <c r="G1"/>
@@ -7395,7 +7236,7 @@
     </row>
     <row r="2" spans="1:12" ht="14.15">
       <c r="A2" s="3" t="s">
-        <v>844</v>
+        <v>809</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
@@ -7407,7 +7248,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>843</v>
+        <v>808</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -7443,7 +7284,7 @@
     </row>
     <row r="4" spans="1:12" ht="14.15">
       <c r="A4" s="5" t="s">
-        <v>872</v>
+        <v>825</v>
       </c>
       <c r="D4" s="7">
         <v>1</v>
@@ -7461,7 +7302,7 @@
     </row>
     <row r="5" spans="1:12" ht="14.15">
       <c r="A5" s="5" t="s">
-        <v>874</v>
+        <v>826</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
@@ -7479,7 +7320,7 @@
     </row>
     <row r="6" spans="1:12" ht="14.15">
       <c r="A6" s="5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D6" s="7">
         <v>1</v>
@@ -7497,7 +7338,7 @@
     </row>
     <row r="7" spans="1:12" ht="14.15">
       <c r="A7" s="5" t="s">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="D7" s="7">
         <v>1</v>
@@ -7515,7 +7356,7 @@
     </row>
     <row r="8" spans="1:12" ht="14.15">
       <c r="A8" s="5" t="s">
-        <v>843</v>
+        <v>808</v>
       </c>
       <c r="B8" s="7">
         <v>45</v>
@@ -7624,7 +7465,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Feuil1"/>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="10.3"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="10" customWidth="1"/>
@@ -7637,8 +7478,11 @@
     <col min="8" max="8" width="13.140625" style="10" customWidth="1"/>
     <col min="9" max="9" width="14.140625" style="10" customWidth="1"/>
     <col min="10" max="10" width="54.5" style="10" customWidth="1"/>
-    <col min="11" max="13" width="44.42578125" style="10" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="10"/>
+    <col min="11" max="12" width="44.42578125" style="10" customWidth="1"/>
+    <col min="13" max="13" width="83.42578125" style="10" customWidth="1"/>
+    <col min="14" max="15" width="9.140625" style="10"/>
+    <col min="16" max="16" width="70.0703125" style="10" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="16" customFormat="1" ht="20.6">
@@ -7673,16 +7517,16 @@
         <v>13</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>877</v>
+        <v>829</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>878</v>
+        <v>830</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="11" customFormat="1" ht="174.9">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="11" customFormat="1" ht="123.45">
       <c r="A2" s="9" t="s">
         <v>14</v>
       </c>
@@ -7702,7 +7546,7 @@
         <v>19</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>861</v>
+        <v>818</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>20</v>
@@ -7714,16 +7558,16 @@
         <v>21</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>880</v>
+        <v>832</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>881</v>
+        <v>833</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="11" customFormat="1" ht="164.6">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="11" customFormat="1" ht="113.15">
       <c r="A3" s="9" t="s">
         <v>22</v>
       </c>
@@ -7743,7 +7587,7 @@
         <v>26</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>862</v>
+        <v>819</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>20</v>
@@ -7755,16 +7599,16 @@
         <v>21</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>883</v>
+        <v>835</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>884</v>
+        <v>836</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="11" customFormat="1" ht="144">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="11" customFormat="1" ht="102.9">
       <c r="A4" s="9" t="s">
         <v>27</v>
       </c>
@@ -7796,16 +7640,16 @@
         <v>21</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>886</v>
+        <v>838</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>887</v>
+        <v>839</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="11" customFormat="1" ht="144">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="11" customFormat="1" ht="113.15">
       <c r="A5" s="9" t="s">
         <v>33</v>
       </c>
@@ -7837,16 +7681,16 @@
         <v>21</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>889</v>
+        <v>841</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>890</v>
+        <v>842</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="11" customFormat="1" ht="195.45">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="11" customFormat="1" ht="133.75">
       <c r="A6" s="9" t="s">
         <v>38</v>
       </c>
@@ -7878,16 +7722,16 @@
         <v>21</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>892</v>
+        <v>844</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>893</v>
+        <v>845</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="11" customFormat="1" ht="195.45">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="11" customFormat="1" ht="133.75">
       <c r="A7" s="9" t="s">
         <v>44</v>
       </c>
@@ -7919,16 +7763,16 @@
         <v>21</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>895</v>
+        <v>847</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>896</v>
+        <v>848</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="11" customFormat="1" ht="164.6">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="11" customFormat="1" ht="123.45">
       <c r="A8" s="9" t="s">
         <v>50</v>
       </c>
@@ -7948,7 +7792,7 @@
         <v>54</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>20</v>
@@ -7960,16 +7804,16 @@
         <v>21</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>898</v>
+        <v>850</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>881</v>
+        <v>833</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="11" customFormat="1" ht="154.30000000000001">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="11" customFormat="1" ht="102.9">
       <c r="A9" s="9" t="s">
         <v>55</v>
       </c>
@@ -8001,16 +7845,16 @@
         <v>21</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>900</v>
+        <v>852</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>901</v>
+        <v>853</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="11" customFormat="1" ht="144">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="11" customFormat="1" ht="113.15">
       <c r="A10" s="9" t="s">
         <v>61</v>
       </c>
@@ -8042,16 +7886,16 @@
         <v>21</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>903</v>
+        <v>855</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>904</v>
+        <v>856</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="11" customFormat="1" ht="92.6">
       <c r="A11" s="9" t="s">
         <v>67</v>
       </c>
@@ -8083,16 +7927,16 @@
         <v>21</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>906</v>
+        <v>858</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>881</v>
+        <v>833</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="11" customFormat="1" ht="92.6">
       <c r="A12" s="9" t="s">
         <v>73</v>
       </c>
@@ -8112,7 +7956,7 @@
         <v>77</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>863</v>
+        <v>1000</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>20</v>
@@ -8124,16 +7968,16 @@
         <v>21</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>908</v>
+        <v>860</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>909</v>
+        <v>861</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="11" customFormat="1" ht="133.75">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="11" customFormat="1" ht="102.9">
       <c r="A13" s="9" t="s">
         <v>78</v>
       </c>
@@ -8153,7 +7997,7 @@
         <v>82</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>864</v>
+        <v>1002</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>20</v>
@@ -8165,16 +8009,16 @@
         <v>21</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>911</v>
+        <v>863</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>912</v>
+        <v>864</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="11" customFormat="1" ht="92.6">
       <c r="A14" s="9" t="s">
         <v>83</v>
       </c>
@@ -8194,7 +8038,7 @@
         <v>87</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>865</v>
+        <v>1003</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>20</v>
@@ -8206,16 +8050,16 @@
         <v>21</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>911</v>
+        <v>863</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>887</v>
+        <v>839</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="11" customFormat="1" ht="92.6">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="11" customFormat="1" ht="72">
       <c r="A15" s="9" t="s">
         <v>88</v>
       </c>
@@ -8235,7 +8079,7 @@
         <v>92</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>93</v>
+        <v>995</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>20</v>
@@ -8244,80 +8088,80 @@
         <v>1</v>
       </c>
       <c r="J15" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>867</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>868</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="102.9">
+      <c r="A16" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>915</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>916</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="113.15">
-      <c r="A16" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="F16" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="G16" s="9" t="s">
-        <v>866</v>
+        <v>820</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>867</v>
+        <v>997</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>868</v>
+        <v>822</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>918</v>
+        <v>870</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>919</v>
+        <v>871</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" s="11" customFormat="1" ht="154.30000000000001">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="11" customFormat="1" ht="102.9">
       <c r="A17" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>104</v>
-      </c>
       <c r="G17" s="9" t="s">
-        <v>105</v>
+        <v>998</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>20</v>
@@ -8326,39 +8170,39 @@
         <v>1</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>921</v>
+        <v>873</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="174.9">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="113.15">
       <c r="A18" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="F18" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>111</v>
-      </c>
       <c r="G18" s="9" t="s">
-        <v>845</v>
+        <v>994</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>20</v>
@@ -8367,39 +8211,39 @@
         <v>2</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>846</v>
+        <v>810</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>924</v>
+        <v>876</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>925</v>
+        <v>877</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="11" customFormat="1" ht="92.6">
       <c r="A19" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>117</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>20</v>
@@ -8408,39 +8252,39 @@
         <v>1</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>927</v>
+        <v>879</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>928</v>
+        <v>880</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="11" customFormat="1" ht="154.30000000000001">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="11" customFormat="1" ht="113.15">
       <c r="A20" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="F20" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="G20" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>20</v>
@@ -8449,39 +8293,39 @@
         <v>1</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>930</v>
+        <v>882</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>881</v>
+        <v>833</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="11" customFormat="1" ht="92.6">
       <c r="A21" s="9" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="F21" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>20</v>
@@ -8490,39 +8334,39 @@
         <v>1</v>
       </c>
       <c r="J21" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>884</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>885</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="11" customFormat="1" ht="102.9">
+      <c r="A22" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="K21" s="13" t="s">
-        <v>932</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>933</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="11" customFormat="1" ht="133.75">
-      <c r="A22" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="G22" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>20</v>
@@ -8531,39 +8375,39 @@
         <v>1</v>
       </c>
       <c r="J22" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>845</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="11" customFormat="1" ht="61.75">
+      <c r="A23" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="K22" s="13" t="s">
-        <v>935</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>893</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" s="11" customFormat="1" ht="82.3">
-      <c r="A23" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="E23" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="G23" s="9" t="s">
         <v>142</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>144</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>20</v>
@@ -8572,39 +8416,39 @@
         <v>1</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>937</v>
+        <v>889</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>887</v>
+        <v>839</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" s="11" customFormat="1" ht="102.9">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="11" customFormat="1" ht="82.3">
       <c r="A24" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>20</v>
@@ -8613,39 +8457,39 @@
         <v>1</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>939</v>
+        <v>891</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>884</v>
+        <v>836</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" s="11" customFormat="1" ht="92.6">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="11" customFormat="1" ht="82.3">
       <c r="A25" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>35</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>20</v>
@@ -8654,39 +8498,39 @@
         <v>1</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>941</v>
+        <v>893</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>890</v>
+        <v>842</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="11" customFormat="1" ht="92.6">
       <c r="A26" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="E26" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="F26" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="G26" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>20</v>
@@ -8695,39 +8539,39 @@
         <v>1</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>943</v>
+        <v>895</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>881</v>
+        <v>833</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="11" customFormat="1" ht="144">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="11" customFormat="1" ht="113.15">
       <c r="A27" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>163</v>
-      </c>
       <c r="G27" s="9" t="s">
-        <v>1040</v>
+        <v>992</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>20</v>
@@ -8736,39 +8580,39 @@
         <v>1</v>
       </c>
       <c r="J27" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>897</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>848</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="11" customFormat="1" ht="82.3">
+      <c r="A28" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="K27" s="13" t="s">
-        <v>945</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>896</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" s="11" customFormat="1" ht="113.15">
-      <c r="A28" s="9" t="s">
+      <c r="E28" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="G28" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>20</v>
@@ -8777,39 +8621,39 @@
         <v>1</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>947</v>
+        <v>899</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>881</v>
+        <v>833</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="11" customFormat="1" ht="92.6">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="11" customFormat="1" ht="72">
       <c r="A29" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="E29" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="F29" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>173</v>
-      </c>
       <c r="G29" s="9" t="s">
-        <v>174</v>
+        <v>993</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>20</v>
@@ -8818,39 +8662,39 @@
         <v>1</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>949</v>
+        <v>901</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>901</v>
+        <v>853</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="144">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="92.6">
       <c r="A30" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>179</v>
-      </c>
       <c r="G30" s="9" t="s">
-        <v>847</v>
+        <v>994</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>20</v>
@@ -8859,39 +8703,39 @@
         <v>2</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>848</v>
+        <v>811</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>951</v>
+        <v>903</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>925</v>
+        <v>877</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" s="11" customFormat="1" ht="92.6">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="11" customFormat="1" ht="72">
       <c r="A31" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>89</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>184</v>
+        <v>995</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>20</v>
@@ -8900,39 +8744,39 @@
         <v>1</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>953</v>
+        <v>905</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>916</v>
+        <v>868</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>954</v>
+        <v>906</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="11" customFormat="1" ht="82.3">
       <c r="A32" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>189</v>
-      </c>
       <c r="G32" s="9" t="s">
-        <v>190</v>
+        <v>996</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>20</v>
@@ -8941,80 +8785,80 @@
         <v>1</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>955</v>
+        <v>907</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>956</v>
+        <v>908</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="92.6">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="72">
       <c r="A33" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>869</v>
+        <v>823</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>195</v>
+        <v>997</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>870</v>
+        <v>824</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>958</v>
+        <v>910</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>919</v>
+        <v>871</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="11" customFormat="1" ht="144">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A34" s="9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>172</v>
-      </c>
       <c r="F34" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>199</v>
+        <v>999</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>20</v>
@@ -9023,39 +8867,39 @@
         <v>1</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>960</v>
+        <v>912</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" s="11" customFormat="1" ht="92.6">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="11" customFormat="1" ht="72">
       <c r="A35" s="9" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>204</v>
+        <v>1001</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>20</v>
@@ -9064,39 +8908,39 @@
         <v>1</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>962</v>
+        <v>914</v>
       </c>
       <c r="L35" s="13" t="s">
-        <v>909</v>
+        <v>861</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="11" customFormat="1" ht="154.30000000000001">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="11" customFormat="1" ht="113.15">
       <c r="A36" s="9" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>211</v>
+        <v>1004</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>20</v>
@@ -9105,39 +8949,39 @@
         <v>1</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>964</v>
+        <v>916</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="164.6">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="133.75">
       <c r="A37" s="9" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>214</v>
-      </c>
       <c r="G37" s="9" t="s">
-        <v>860</v>
+        <v>1005</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>20</v>
@@ -9146,39 +8990,39 @@
         <v>2</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>849</v>
+        <v>812</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>967</v>
+        <v>919</v>
       </c>
       <c r="L37" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A38" s="9" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>218</v>
+        <v>1006</v>
       </c>
       <c r="H38" s="9" t="s">
         <v>20</v>
@@ -9187,39 +9031,39 @@
         <v>1</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>969</v>
+        <v>921</v>
       </c>
       <c r="L38" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" s="11" customFormat="1" ht="133.75">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A39" s="9" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>222</v>
+        <v>1007</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>20</v>
@@ -9228,39 +9072,39 @@
         <v>1</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>971</v>
+        <v>923</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A40" s="9" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>226</v>
+        <v>1008</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>20</v>
@@ -9269,39 +9113,39 @@
         <v>1</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>973</v>
+        <v>925</v>
       </c>
       <c r="L40" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A41" s="9" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>231</v>
+        <v>1009</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>20</v>
@@ -9310,39 +9154,39 @@
         <v>1</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>975</v>
+        <v>927</v>
       </c>
       <c r="L41" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" s="11" customFormat="1" ht="102.9">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A42" s="9" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>236</v>
+        <v>1009</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>20</v>
@@ -9351,39 +9195,39 @@
         <v>1</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>977</v>
+        <v>929</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A43" s="9" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>241</v>
+        <v>1010</v>
       </c>
       <c r="H43" s="9" t="s">
         <v>20</v>
@@ -9392,39 +9236,39 @@
         <v>1</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>979</v>
+        <v>931</v>
       </c>
       <c r="L43" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A44" s="9" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>246</v>
+        <v>1011</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>20</v>
@@ -9433,39 +9277,39 @@
         <v>1</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>981</v>
+        <v>933</v>
       </c>
       <c r="L44" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A45" s="9" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>251</v>
+        <v>1012</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>20</v>
@@ -9474,39 +9318,39 @@
         <v>1</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>983</v>
+        <v>935</v>
       </c>
       <c r="L45" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M45" s="9" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A46" s="9" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>255</v>
+        <v>1013</v>
       </c>
       <c r="H46" s="9" t="s">
         <v>20</v>
@@ -9515,39 +9359,39 @@
         <v>1</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>985</v>
+        <v>937</v>
       </c>
       <c r="L46" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="113.15">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="82.3">
       <c r="A47" s="9" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>850</v>
+        <v>1014</v>
       </c>
       <c r="H47" s="9" t="s">
         <v>20</v>
@@ -9556,39 +9400,45 @@
         <v>2</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>851</v>
+        <v>813</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>987</v>
+        <v>939</v>
       </c>
       <c r="L47" s="13" t="s">
-        <v>965</v>
+        <v>917</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" s="11" customFormat="1" ht="144">
+        <v>940</v>
+      </c>
+      <c r="O47" s="17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="P47" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" s="11" customFormat="1" ht="102.9">
       <c r="A48" s="9" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>265</v>
+        <v>1016</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>20</v>
@@ -9597,39 +9447,45 @@
         <v>1</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>989</v>
+        <v>941</v>
       </c>
       <c r="L48" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" s="11" customFormat="1" ht="133.75">
+        <v>943</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="P48" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A49" s="9" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>269</v>
+        <v>1016</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>20</v>
@@ -9638,39 +9494,45 @@
         <v>1</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>992</v>
+        <v>944</v>
       </c>
       <c r="L49" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="123.45">
+        <v>945</v>
+      </c>
+      <c r="O49" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="P49" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="82.3">
       <c r="A50" s="9" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>852</v>
+        <v>1016</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>20</v>
@@ -9679,39 +9541,45 @@
         <v>2</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>853</v>
+        <v>814</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>994</v>
+        <v>946</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>947</v>
+      </c>
+      <c r="O50" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="P50" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A51" s="9" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>276</v>
+        <v>1016</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>20</v>
@@ -9720,39 +9588,45 @@
         <v>1</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>996</v>
+        <v>948</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>949</v>
+      </c>
+      <c r="O51" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="P51" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A52" s="9" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>280</v>
+        <v>1016</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>20</v>
@@ -9761,39 +9635,45 @@
         <v>1</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>998</v>
+        <v>950</v>
       </c>
       <c r="L52" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>951</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="P52" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A53" s="9" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C53" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>282</v>
-      </c>
       <c r="E53" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>284</v>
+        <v>1016</v>
       </c>
       <c r="H53" s="9" t="s">
         <v>20</v>
@@ -9802,39 +9682,45 @@
         <v>1</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>1000</v>
+        <v>952</v>
       </c>
       <c r="L53" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>953</v>
+      </c>
+      <c r="O53" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="P53" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A54" s="9" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>288</v>
+        <v>1016</v>
       </c>
       <c r="H54" s="9" t="s">
         <v>20</v>
@@ -9843,39 +9729,45 @@
         <v>1</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>1002</v>
+        <v>954</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>955</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="P54" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A55" s="9" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>292</v>
+        <v>1016</v>
       </c>
       <c r="H55" s="9" t="s">
         <v>20</v>
@@ -9884,39 +9776,45 @@
         <v>1</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>1004</v>
+        <v>956</v>
       </c>
       <c r="L55" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" s="11" customFormat="1" ht="133.75">
+        <v>957</v>
+      </c>
+      <c r="O55" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="P55" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A56" s="9" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>296</v>
+        <v>1016</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>20</v>
@@ -9925,39 +9823,45 @@
         <v>1</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>1006</v>
+        <v>958</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>959</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="P56" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A57" s="9" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>300</v>
+        <v>1016</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>20</v>
@@ -9966,39 +9870,45 @@
         <v>1</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>1008</v>
+        <v>960</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>961</v>
+      </c>
+      <c r="O57" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="P57" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A58" s="9" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>304</v>
+        <v>1016</v>
       </c>
       <c r="H58" s="9" t="s">
         <v>20</v>
@@ -10007,80 +9917,92 @@
         <v>1</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>1010</v>
+        <v>962</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M58" s="9" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="102.9">
+        <v>963</v>
+      </c>
+      <c r="O58" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="P58" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="72">
       <c r="A59" s="9" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>871</v>
+        <v>1016</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>872</v>
+        <v>825</v>
       </c>
       <c r="I59" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="K59" s="13" t="s">
-        <v>1012</v>
+        <v>964</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>1013</v>
+        <v>965</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>966</v>
+      </c>
+      <c r="O59" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="P59" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A60" s="9" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>312</v>
+        <v>1016</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>20</v>
@@ -10089,39 +10011,45 @@
         <v>1</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>1015</v>
+        <v>967</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M60" s="9" t="s">
+        <v>968</v>
+      </c>
+      <c r="O60" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="P60" s="9" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="11" customFormat="1" ht="133.75">
+    <row r="61" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A61" s="9" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>316</v>
+        <v>1016</v>
       </c>
       <c r="H61" s="9" t="s">
         <v>20</v>
@@ -10130,39 +10058,45 @@
         <v>1</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K61" s="13" t="s">
-        <v>1017</v>
+        <v>969</v>
       </c>
       <c r="L61" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>970</v>
+      </c>
+      <c r="O61" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="P61" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A62" s="9" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>320</v>
+        <v>1016</v>
       </c>
       <c r="H62" s="9" t="s">
         <v>20</v>
@@ -10171,39 +10105,45 @@
         <v>1</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>1019</v>
+        <v>971</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>972</v>
+      </c>
+      <c r="O62" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="P62" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A63" s="9" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>324</v>
+        <v>1016</v>
       </c>
       <c r="H63" s="9" t="s">
         <v>20</v>
@@ -10212,39 +10152,45 @@
         <v>1</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>1021</v>
+        <v>973</v>
       </c>
       <c r="L63" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" s="11" customFormat="1" ht="113.15">
+        <v>974</v>
+      </c>
+      <c r="O63" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="P63" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A64" s="9" t="s">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>328</v>
+        <v>1016</v>
       </c>
       <c r="H64" s="9" t="s">
         <v>20</v>
@@ -10253,39 +10199,45 @@
         <v>1</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>1023</v>
+        <v>975</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" s="11" customFormat="1" ht="133.75">
+        <v>976</v>
+      </c>
+      <c r="O64" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="P64" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" s="11" customFormat="1" ht="92.6">
       <c r="A65" s="9" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>332</v>
+        <v>1016</v>
       </c>
       <c r="H65" s="9" t="s">
         <v>20</v>
@@ -10294,39 +10246,45 @@
         <v>1</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>1025</v>
+        <v>977</v>
       </c>
       <c r="L65" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>978</v>
+      </c>
+      <c r="O65" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="P65" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A66" s="9" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>336</v>
+        <v>1016</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>20</v>
@@ -10335,39 +10293,45 @@
         <v>1</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>1027</v>
+        <v>979</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="102.9">
+        <v>980</v>
+      </c>
+      <c r="O66" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="P66" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="72">
       <c r="A67" s="9" t="s">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>854</v>
+        <v>1016</v>
       </c>
       <c r="H67" s="9" t="s">
         <v>20</v>
@@ -10376,39 +10340,45 @@
         <v>2</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>855</v>
+        <v>815</v>
       </c>
       <c r="K67" s="13" t="s">
-        <v>1029</v>
+        <v>981</v>
       </c>
       <c r="L67" s="13" t="s">
-        <v>1030</v>
+        <v>982</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" s="11" customFormat="1" ht="123.45">
+        <v>983</v>
+      </c>
+      <c r="O67" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="P67" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" s="11" customFormat="1" ht="82.3">
       <c r="A68" s="9" t="s">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>343</v>
+        <v>1016</v>
       </c>
       <c r="H68" s="9" t="s">
         <v>20</v>
@@ -10417,39 +10387,45 @@
         <v>1</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>1032</v>
+        <v>984</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="133.75">
+        <v>985</v>
+      </c>
+      <c r="O68" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="P68" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="92.6">
       <c r="A69" s="9" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>856</v>
+        <v>1016</v>
       </c>
       <c r="H69" s="9" t="s">
         <v>20</v>
@@ -10458,80 +10434,92 @@
         <v>2</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>857</v>
+        <v>816</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>1034</v>
+        <v>986</v>
       </c>
       <c r="L69" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M69" s="9" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="123.45">
+        <v>987</v>
+      </c>
+      <c r="O69" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="P69" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="82.3">
       <c r="A70" s="9" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>873</v>
+        <v>1016</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>874</v>
+        <v>826</v>
       </c>
       <c r="I70" s="9" t="s">
         <v>3</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>875</v>
+        <v>827</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>1036</v>
+        <v>988</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M70" s="9" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="164.6">
+        <v>989</v>
+      </c>
+      <c r="O70" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="P70" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="102.9">
       <c r="A71" s="9" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>858</v>
+        <v>1016</v>
       </c>
       <c r="H71" s="9" t="s">
         <v>20</v>
@@ -10540,43 +10528,49 @@
         <v>2</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>859</v>
+        <v>817</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>1038</v>
+        <v>990</v>
       </c>
       <c r="L71" s="13" t="s">
-        <v>990</v>
+        <v>942</v>
       </c>
       <c r="M71" s="9" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+        <v>991</v>
+      </c>
+      <c r="O71" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="P71" s="9" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" s="8"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="K73" s="9"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:16">
       <c r="A74" s="8"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="K74" s="9"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:16">
       <c r="A75" s="8"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="K75" s="9"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:16">
       <c r="A76" s="8"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:16">
       <c r="A77" s="8"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
@@ -10603,3582 +10597,3582 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>354</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>448</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>449</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>450</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="2" t="s">
-        <v>451</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>452</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="2" t="s">
-        <v>453</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>454</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
-        <v>456</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>457</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="2" t="s">
-        <v>458</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="2" t="s">
-        <v>459</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="2" t="s">
-        <v>460</v>
+        <v>425</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>461</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>463</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>464</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="2" t="s">
-        <v>465</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="2" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="2" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>470</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="2" t="s">
-        <v>472</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>474</v>
+        <v>439</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="2" t="s">
-        <v>475</v>
+        <v>440</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>476</v>
+        <v>441</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>477</v>
+        <v>442</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="2" t="s">
-        <v>478</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>479</v>
+        <v>444</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>480</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>482</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="2" t="s">
-        <v>483</v>
+        <v>448</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>484</v>
+        <v>449</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>485</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>486</v>
+        <v>451</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>487</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>488</v>
+        <v>453</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>489</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>490</v>
+        <v>455</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>492</v>
+        <v>457</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>493</v>
+        <v>458</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>494</v>
+        <v>459</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="2" t="s">
-        <v>495</v>
+        <v>460</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="2" t="s">
-        <v>497</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="2" t="s">
-        <v>498</v>
+        <v>463</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>501</v>
+        <v>466</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="2" t="s">
-        <v>502</v>
+        <v>467</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>503</v>
+        <v>468</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>504</v>
+        <v>469</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>505</v>
+        <v>470</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>506</v>
+        <v>471</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="2" t="s">
-        <v>507</v>
+        <v>472</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>508</v>
+        <v>473</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="2" t="s">
-        <v>509</v>
+        <v>474</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="2" t="s">
-        <v>510</v>
+        <v>475</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>511</v>
+        <v>476</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>512</v>
+        <v>477</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="2" t="s">
-        <v>513</v>
+        <v>478</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>514</v>
+        <v>479</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="2" t="s">
-        <v>515</v>
+        <v>480</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
-        <v>516</v>
+        <v>481</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>517</v>
+        <v>482</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>518</v>
+        <v>483</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="2" t="s">
-        <v>519</v>
+        <v>484</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>520</v>
+        <v>485</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>521</v>
+        <v>486</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>522</v>
+        <v>487</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="2" t="s">
-        <v>523</v>
+        <v>488</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="2" t="s">
-        <v>524</v>
+        <v>489</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>525</v>
+        <v>490</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="2" t="s">
-        <v>526</v>
+        <v>491</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="2" t="s">
-        <v>527</v>
+        <v>492</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="2" t="s">
-        <v>528</v>
+        <v>493</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>529</v>
+        <v>494</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="2" t="s">
-        <v>530</v>
+        <v>495</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>531</v>
+        <v>496</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="2" t="s">
-        <v>532</v>
+        <v>497</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>533</v>
+        <v>498</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="2" t="s">
-        <v>535</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="2" t="s">
-        <v>536</v>
+        <v>501</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="2" t="s">
-        <v>537</v>
+        <v>502</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="2" t="s">
-        <v>538</v>
+        <v>503</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>539</v>
+        <v>504</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="2" t="s">
-        <v>540</v>
+        <v>505</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>541</v>
+        <v>506</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="2" t="s">
-        <v>542</v>
+        <v>507</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="2" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="2" t="s">
-        <v>544</v>
+        <v>509</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="2" t="s">
-        <v>545</v>
+        <v>510</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="2" t="s">
-        <v>546</v>
+        <v>511</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="2" t="s">
-        <v>547</v>
+        <v>512</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="2" t="s">
-        <v>548</v>
+        <v>513</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="2" t="s">
-        <v>549</v>
+        <v>514</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>550</v>
+        <v>515</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="2" t="s">
-        <v>551</v>
+        <v>516</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="2" t="s">
-        <v>552</v>
+        <v>517</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="2" t="s">
-        <v>553</v>
+        <v>518</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="2" t="s">
-        <v>554</v>
+        <v>519</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>555</v>
+        <v>520</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="2" t="s">
-        <v>556</v>
+        <v>521</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="2" t="s">
-        <v>557</v>
+        <v>522</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="2" t="s">
-        <v>558</v>
+        <v>523</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="2" t="s">
-        <v>559</v>
+        <v>524</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="2" t="s">
-        <v>560</v>
+        <v>525</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="2" t="s">
-        <v>561</v>
+        <v>526</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="2" t="s">
-        <v>562</v>
+        <v>527</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="2" t="s">
-        <v>563</v>
+        <v>528</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="2" t="s">
-        <v>564</v>
+        <v>529</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>565</v>
+        <v>530</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="2" t="s">
-        <v>566</v>
+        <v>531</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="2" t="s">
-        <v>567</v>
+        <v>532</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>568</v>
+        <v>533</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="2" t="s">
-        <v>569</v>
+        <v>534</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="2" t="s">
-        <v>570</v>
+        <v>535</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="2" t="s">
-        <v>571</v>
+        <v>536</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="2" t="s">
-        <v>572</v>
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="2" t="s">
-        <v>573</v>
+        <v>538</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>574</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="2" t="s">
-        <v>575</v>
+        <v>540</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="2" t="s">
-        <v>576</v>
+        <v>541</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="2" t="s">
-        <v>577</v>
+        <v>542</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="2" t="s">
-        <v>578</v>
+        <v>543</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="2" t="s">
-        <v>579</v>
+        <v>544</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="2" t="s">
-        <v>580</v>
+        <v>545</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="2" t="s">
-        <v>581</v>
+        <v>546</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>582</v>
+        <v>547</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="2" t="s">
-        <v>583</v>
+        <v>548</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="2" t="s">
-        <v>584</v>
+        <v>549</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="2" t="s">
-        <v>585</v>
+        <v>550</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="2" t="s">
-        <v>586</v>
+        <v>551</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="2" t="s">
-        <v>587</v>
+        <v>552</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>588</v>
+        <v>553</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="2" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="2" t="s">
-        <v>590</v>
+        <v>555</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="2" t="s">
-        <v>578</v>
+        <v>543</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>591</v>
+        <v>556</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="2" t="s">
-        <v>592</v>
+        <v>557</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="2" t="s">
-        <v>593</v>
+        <v>558</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="2" t="s">
-        <v>594</v>
+        <v>559</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="2" t="s">
-        <v>595</v>
+        <v>560</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="2" t="s">
-        <v>596</v>
+        <v>561</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="2" t="s">
-        <v>597</v>
+        <v>562</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="2" t="s">
-        <v>578</v>
+        <v>543</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="2" t="s">
-        <v>598</v>
+        <v>563</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="2" t="s">
-        <v>599</v>
+        <v>564</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>600</v>
+        <v>565</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="2" t="s">
-        <v>601</v>
+        <v>566</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>602</v>
+        <v>567</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="2" t="s">
-        <v>603</v>
+        <v>568</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="2" t="s">
-        <v>604</v>
+        <v>569</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="2" t="s">
-        <v>605</v>
+        <v>570</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="2" t="s">
-        <v>606</v>
+        <v>571</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="2" t="s">
-        <v>607</v>
+        <v>572</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>608</v>
+        <v>573</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="2" t="s">
-        <v>609</v>
+        <v>574</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="2" t="s">
-        <v>610</v>
+        <v>575</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="2" t="s">
-        <v>611</v>
+        <v>576</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="2" t="s">
-        <v>612</v>
+        <v>577</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="2" t="s">
-        <v>613</v>
+        <v>578</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="2" t="s">
-        <v>614</v>
+        <v>579</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="2" t="s">
-        <v>615</v>
+        <v>580</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="2" t="s">
-        <v>616</v>
+        <v>581</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="2" t="s">
-        <v>617</v>
+        <v>582</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>618</v>
+        <v>583</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="2" t="s">
-        <v>619</v>
+        <v>584</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="2" t="s">
-        <v>620</v>
+        <v>585</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="2" t="s">
-        <v>621</v>
+        <v>586</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="2" t="s">
-        <v>622</v>
+        <v>587</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="2" t="s">
-        <v>623</v>
+        <v>588</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="2" t="s">
-        <v>624</v>
+        <v>589</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="2" t="s">
-        <v>625</v>
+        <v>590</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="2" t="s">
-        <v>626</v>
+        <v>591</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="2" t="s">
-        <v>627</v>
+        <v>592</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="2" t="s">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>629</v>
+        <v>594</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="2" t="s">
-        <v>630</v>
+        <v>595</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="2" t="s">
-        <v>631</v>
+        <v>596</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="2" t="s">
-        <v>632</v>
+        <v>597</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="2" t="s">
-        <v>633</v>
+        <v>598</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="2" t="s">
-        <v>634</v>
+        <v>599</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>635</v>
+        <v>600</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="2" t="s">
-        <v>636</v>
+        <v>601</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="2" t="s">
-        <v>637</v>
+        <v>602</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="2" t="s">
-        <v>638</v>
+        <v>603</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="2" t="s">
-        <v>639</v>
+        <v>604</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="2" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="2" t="s">
-        <v>641</v>
+        <v>606</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="2" t="s">
-        <v>642</v>
+        <v>607</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="2" t="s">
-        <v>643</v>
+        <v>608</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="2" t="s">
-        <v>644</v>
+        <v>609</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="2" t="s">
-        <v>645</v>
+        <v>610</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="2" t="s">
-        <v>646</v>
+        <v>611</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="2" t="s">
-        <v>647</v>
+        <v>612</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="2" t="s">
-        <v>648</v>
+        <v>613</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="2" t="s">
-        <v>649</v>
+        <v>614</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="2" t="s">
-        <v>650</v>
+        <v>615</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="2" t="s">
-        <v>651</v>
+        <v>616</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="2" t="s">
-        <v>652</v>
+        <v>617</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="2" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="2" t="s">
-        <v>654</v>
+        <v>619</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="2" t="s">
-        <v>655</v>
+        <v>620</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="2" t="s">
-        <v>656</v>
+        <v>621</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="2" t="s">
-        <v>657</v>
+        <v>622</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="2" t="s">
-        <v>658</v>
+        <v>623</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="2" t="s">
-        <v>659</v>
+        <v>624</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="2" t="s">
-        <v>660</v>
+        <v>625</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="2" t="s">
-        <v>661</v>
+        <v>626</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="2" t="s">
-        <v>662</v>
+        <v>627</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="2" t="s">
-        <v>662</v>
+        <v>627</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" s="2" t="s">
-        <v>664</v>
+        <v>629</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="2" t="s">
-        <v>666</v>
+        <v>631</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="2" t="s">
-        <v>671</v>
+        <v>636</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="2" t="s">
-        <v>672</v>
+        <v>637</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="2" t="s">
-        <v>673</v>
+        <v>638</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="2" t="s">
-        <v>674</v>
+        <v>639</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="2" t="s">
-        <v>675</v>
+        <v>640</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="2" t="s">
-        <v>676</v>
+        <v>641</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="2" t="s">
-        <v>677</v>
+        <v>642</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="2" t="s">
-        <v>678</v>
+        <v>643</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="2" t="s">
-        <v>679</v>
+        <v>644</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="2" t="s">
-        <v>680</v>
+        <v>645</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="2" t="s">
-        <v>681</v>
+        <v>646</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="2" t="s">
-        <v>682</v>
+        <v>647</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="2" t="s">
-        <v>683</v>
+        <v>648</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="2" t="s">
-        <v>684</v>
+        <v>649</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="2" t="s">
-        <v>637</v>
+        <v>602</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="2" t="s">
-        <v>685</v>
+        <v>650</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="2" t="s">
-        <v>686</v>
+        <v>651</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="2" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="2" t="s">
-        <v>687</v>
+        <v>652</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="2" t="s">
-        <v>688</v>
+        <v>653</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="2" t="s">
-        <v>689</v>
+        <v>654</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="2" t="s">
-        <v>644</v>
+        <v>609</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="2" t="s">
-        <v>690</v>
+        <v>655</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="2" t="s">
-        <v>691</v>
+        <v>656</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="2" t="s">
-        <v>692</v>
+        <v>657</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="2" t="s">
-        <v>693</v>
+        <v>658</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="2" t="s">
-        <v>647</v>
+        <v>612</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="2" t="s">
-        <v>694</v>
+        <v>659</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="2" t="s">
-        <v>695</v>
+        <v>660</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="2" t="s">
-        <v>696</v>
+        <v>661</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="2" t="s">
-        <v>697</v>
+        <v>662</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="2" t="s">
-        <v>651</v>
+        <v>616</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="2" t="s">
-        <v>652</v>
+        <v>617</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="2" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" s="2" t="s">
-        <v>698</v>
+        <v>663</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" s="2" t="s">
-        <v>699</v>
+        <v>664</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="2" t="s">
-        <v>700</v>
+        <v>665</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="2" t="s">
-        <v>701</v>
+        <v>666</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" s="2" t="s">
-        <v>658</v>
+        <v>623</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="2" t="s">
-        <v>702</v>
+        <v>667</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="2" t="s">
-        <v>703</v>
+        <v>668</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="2" t="s">
-        <v>704</v>
+        <v>669</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="2" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="2" t="s">
-        <v>706</v>
+        <v>671</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" s="2" t="s">
-        <v>707</v>
+        <v>672</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" s="2" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" s="2" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" s="2" t="s">
-        <v>710</v>
+        <v>675</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" s="2" t="s">
-        <v>711</v>
+        <v>676</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" s="2" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" s="2" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" s="2" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" s="2" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" s="2" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
     </row>
     <row r="330" spans="1:1">
       <c r="A330" s="2" t="s">
-        <v>718</v>
+        <v>683</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" s="2" t="s">
-        <v>719</v>
+        <v>684</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" s="2" t="s">
-        <v>720</v>
+        <v>685</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" s="2" t="s">
-        <v>721</v>
+        <v>686</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" s="2" t="s">
-        <v>722</v>
+        <v>687</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" s="2" t="s">
-        <v>723</v>
+        <v>688</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" s="2" t="s">
-        <v>724</v>
+        <v>689</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="343" spans="1:1">
       <c r="A343" s="2" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
     </row>
     <row r="344" spans="1:1">
       <c r="A344" s="2" t="s">
-        <v>725</v>
+        <v>690</v>
       </c>
     </row>
     <row r="345" spans="1:1">
       <c r="A345" s="2" t="s">
-        <v>726</v>
+        <v>691</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346" s="2" t="s">
-        <v>727</v>
+        <v>692</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348" s="2" t="s">
-        <v>725</v>
+        <v>690</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349" s="2" t="s">
-        <v>726</v>
+        <v>691</v>
       </c>
     </row>
     <row r="350" spans="1:1">
       <c r="A350" s="2" t="s">
-        <v>727</v>
+        <v>692</v>
       </c>
     </row>
     <row r="353" spans="1:1">
       <c r="A353" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355" s="2" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
     </row>
     <row r="356" spans="1:1">
       <c r="A356" s="2" t="s">
-        <v>728</v>
+        <v>693</v>
       </c>
     </row>
     <row r="357" spans="1:1">
       <c r="A357" s="2" t="s">
-        <v>729</v>
+        <v>694</v>
       </c>
     </row>
     <row r="358" spans="1:1">
       <c r="A358" s="2" t="s">
-        <v>730</v>
+        <v>695</v>
       </c>
     </row>
     <row r="360" spans="1:1">
       <c r="A360" s="2" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
     </row>
     <row r="361" spans="1:1">
       <c r="A361" s="2" t="s">
-        <v>360</v>
+        <v>325</v>
       </c>
     </row>
     <row r="362" spans="1:1">
       <c r="A362" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="363" spans="1:1">
       <c r="A363" s="2" t="s">
-        <v>731</v>
+        <v>696</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" s="2" t="s">
-        <v>732</v>
+        <v>697</v>
       </c>
     </row>
     <row r="365" spans="1:1">
       <c r="A365" s="2" t="s">
-        <v>733</v>
+        <v>698</v>
       </c>
     </row>
     <row r="366" spans="1:1">
       <c r="A366" s="2" t="s">
-        <v>734</v>
+        <v>699</v>
       </c>
     </row>
     <row r="367" spans="1:1">
       <c r="A367" s="2" t="s">
-        <v>735</v>
+        <v>700</v>
       </c>
     </row>
     <row r="368" spans="1:1">
       <c r="A368" s="2" t="s">
-        <v>736</v>
+        <v>701</v>
       </c>
     </row>
     <row r="370" spans="1:1">
       <c r="A370" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" s="2" t="s">
-        <v>737</v>
+        <v>702</v>
       </c>
     </row>
     <row r="372" spans="1:1">
       <c r="A372" s="2" t="s">
-        <v>738</v>
+        <v>703</v>
       </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" s="2" t="s">
-        <v>739</v>
+        <v>704</v>
       </c>
     </row>
     <row r="374" spans="1:1">
       <c r="A374" s="2" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
     </row>
     <row r="376" spans="1:1">
       <c r="A376" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377" s="2" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378" s="2" t="s">
-        <v>742</v>
+        <v>707</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" s="2" t="s">
-        <v>743</v>
+        <v>708</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380" s="2" t="s">
-        <v>744</v>
+        <v>709</v>
       </c>
     </row>
     <row r="381" spans="1:1">
       <c r="A381" s="2" t="s">
-        <v>745</v>
+        <v>710</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382" s="2" t="s">
-        <v>746</v>
+        <v>711</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383" s="2" t="s">
-        <v>747</v>
+        <v>712</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385" s="2" t="s">
-        <v>748</v>
+        <v>713</v>
       </c>
     </row>
     <row r="386" spans="1:1">
       <c r="A386" s="2" t="s">
-        <v>749</v>
+        <v>714</v>
       </c>
     </row>
     <row r="387" spans="1:1">
       <c r="A387" s="2" t="s">
-        <v>750</v>
+        <v>715</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="391" spans="1:1">
       <c r="A391" s="2" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
     </row>
     <row r="392" spans="1:1">
       <c r="A392" s="2" t="s">
-        <v>751</v>
+        <v>716</v>
       </c>
     </row>
     <row r="393" spans="1:1">
       <c r="A393" s="2" t="s">
-        <v>752</v>
+        <v>717</v>
       </c>
     </row>
     <row r="394" spans="1:1">
       <c r="A394" s="2" t="s">
-        <v>753</v>
+        <v>718</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396" s="2" t="s">
-        <v>754</v>
+        <v>719</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397" s="2" t="s">
-        <v>755</v>
+        <v>720</v>
       </c>
     </row>
     <row r="398" spans="1:1">
       <c r="A398" s="2" t="s">
-        <v>756</v>
+        <v>721</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399" s="2" t="s">
-        <v>757</v>
+        <v>722</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401" s="2" t="s">
-        <v>748</v>
+        <v>713</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" s="2" t="s">
-        <v>749</v>
+        <v>714</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" s="2" t="s">
-        <v>750</v>
+        <v>715</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="407" spans="1:1">
       <c r="A407" s="2" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
     </row>
     <row r="408" spans="1:1">
       <c r="A408" s="2" t="s">
-        <v>751</v>
+        <v>716</v>
       </c>
     </row>
     <row r="409" spans="1:1">
       <c r="A409" s="2" t="s">
-        <v>758</v>
+        <v>723</v>
       </c>
     </row>
     <row r="411" spans="1:1">
       <c r="A411" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" s="2" t="s">
-        <v>361</v>
+        <v>326</v>
       </c>
     </row>
     <row r="414" spans="1:1">
       <c r="A414" s="2" t="s">
-        <v>722</v>
+        <v>687</v>
       </c>
     </row>
     <row r="415" spans="1:1">
       <c r="A415" s="2" t="s">
-        <v>759</v>
+        <v>724</v>
       </c>
     </row>
     <row r="416" spans="1:1">
       <c r="A416" s="2" t="s">
-        <v>760</v>
+        <v>725</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" s="2" t="s">
-        <v>724</v>
+        <v>689</v>
       </c>
     </row>
     <row r="420" spans="1:1">
       <c r="A420" s="2" t="s">
-        <v>724</v>
+        <v>689</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" s="2" t="s">
-        <v>724</v>
+        <v>689</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" s="2" t="s">
-        <v>721</v>
+        <v>686</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" s="2" t="s">
-        <v>362</v>
+        <v>327</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" s="2" t="s">
-        <v>761</v>
+        <v>726</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" s="2" t="s">
-        <v>762</v>
+        <v>727</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" s="2" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" s="2" t="s">
-        <v>706</v>
+        <v>671</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" s="2" t="s">
-        <v>707</v>
+        <v>672</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" s="2" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" s="2" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="440" spans="1:1">
       <c r="A440" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="441" spans="1:1">
       <c r="A441" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="442" spans="1:1">
       <c r="A442" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="443" spans="1:1">
       <c r="A443" s="2" t="s">
-        <v>710</v>
+        <v>675</v>
       </c>
     </row>
     <row r="444" spans="1:1">
       <c r="A444" s="2" t="s">
-        <v>711</v>
+        <v>676</v>
       </c>
     </row>
     <row r="445" spans="1:1">
       <c r="A445" s="2" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
     </row>
     <row r="446" spans="1:1">
       <c r="A446" s="2" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
     </row>
     <row r="448" spans="1:1">
       <c r="A448" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="449" spans="1:1">
       <c r="A449" s="2" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
     </row>
     <row r="450" spans="1:1">
       <c r="A450" s="2" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
     </row>
     <row r="451" spans="1:1">
       <c r="A451" s="2" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
     </row>
     <row r="452" spans="1:1">
       <c r="A452" s="2" t="s">
-        <v>718</v>
+        <v>683</v>
       </c>
     </row>
     <row r="454" spans="1:1">
       <c r="A454" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="455" spans="1:1">
       <c r="A455" s="2" t="s">
-        <v>719</v>
+        <v>684</v>
       </c>
     </row>
     <row r="456" spans="1:1">
       <c r="A456" s="2" t="s">
-        <v>763</v>
+        <v>728</v>
       </c>
     </row>
     <row r="457" spans="1:1">
       <c r="A457" s="2" t="s">
-        <v>764</v>
+        <v>729</v>
       </c>
     </row>
     <row r="458" spans="1:1">
       <c r="A458" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
     </row>
     <row r="459" spans="1:1">
       <c r="A459" s="2" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
     </row>
     <row r="460" spans="1:1">
       <c r="A460" s="2" t="s">
-        <v>757</v>
+        <v>722</v>
       </c>
     </row>
     <row r="462" spans="1:1">
       <c r="A462" s="2" t="s">
-        <v>720</v>
+        <v>685</v>
       </c>
     </row>
     <row r="463" spans="1:1">
       <c r="A463" s="2" t="s">
-        <v>721</v>
+        <v>686</v>
       </c>
     </row>
     <row r="465" spans="1:1">
       <c r="A465" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="467" spans="1:1">
       <c r="A467" s="2" t="s">
-        <v>363</v>
+        <v>328</v>
       </c>
     </row>
     <row r="468" spans="1:1">
       <c r="A468" s="2" t="s">
-        <v>767</v>
+        <v>732</v>
       </c>
     </row>
     <row r="470" spans="1:1">
       <c r="A470" s="2" t="s">
-        <v>364</v>
+        <v>329</v>
       </c>
     </row>
     <row r="471" spans="1:1">
       <c r="A471" s="2" t="s">
-        <v>360</v>
+        <v>325</v>
       </c>
     </row>
     <row r="472" spans="1:1">
       <c r="A472" s="2" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
     </row>
     <row r="473" spans="1:1">
       <c r="A473" s="2" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
     </row>
     <row r="475" spans="1:1">
       <c r="A475" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="476" spans="1:1">
       <c r="A476" s="2" t="s">
-        <v>706</v>
+        <v>671</v>
       </c>
     </row>
     <row r="477" spans="1:1">
       <c r="A477" s="2" t="s">
-        <v>707</v>
+        <v>672</v>
       </c>
     </row>
     <row r="478" spans="1:1">
       <c r="A478" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="479" spans="1:1">
       <c r="A479" s="2" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
     </row>
     <row r="480" spans="1:1">
       <c r="A480" s="2" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
     </row>
     <row r="481" spans="1:1">
       <c r="A481" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="483" spans="1:1">
       <c r="A483" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="484" spans="1:1">
       <c r="A484" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="485" spans="1:1">
       <c r="A485" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="486" spans="1:1">
       <c r="A486" s="2" t="s">
-        <v>710</v>
+        <v>675</v>
       </c>
     </row>
     <row r="487" spans="1:1">
       <c r="A487" s="2" t="s">
-        <v>711</v>
+        <v>676</v>
       </c>
     </row>
     <row r="488" spans="1:1">
       <c r="A488" s="2" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
     </row>
     <row r="489" spans="1:1">
       <c r="A489" s="2" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
     </row>
     <row r="491" spans="1:1">
       <c r="A491" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="492" spans="1:1">
       <c r="A492" s="2" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
     </row>
     <row r="493" spans="1:1">
       <c r="A493" s="2" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
     </row>
     <row r="494" spans="1:1">
       <c r="A494" s="2" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
     </row>
     <row r="495" spans="1:1">
       <c r="A495" s="2" t="s">
-        <v>718</v>
+        <v>683</v>
       </c>
     </row>
     <row r="497" spans="1:1">
       <c r="A497" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="498" spans="1:1">
       <c r="A498" s="2" t="s">
-        <v>719</v>
+        <v>684</v>
       </c>
     </row>
     <row r="499" spans="1:1">
       <c r="A499" s="2" t="s">
-        <v>763</v>
+        <v>728</v>
       </c>
     </row>
     <row r="500" spans="1:1">
       <c r="A500" s="2" t="s">
-        <v>764</v>
+        <v>729</v>
       </c>
     </row>
     <row r="501" spans="1:1">
       <c r="A501" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
     </row>
     <row r="502" spans="1:1">
       <c r="A502" s="2" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
     </row>
     <row r="503" spans="1:1">
       <c r="A503" s="2" t="s">
-        <v>757</v>
+        <v>722</v>
       </c>
     </row>
     <row r="505" spans="1:1">
       <c r="A505" s="2" t="s">
-        <v>720</v>
+        <v>685</v>
       </c>
     </row>
     <row r="506" spans="1:1">
       <c r="A506" s="2" t="s">
-        <v>721</v>
+        <v>686</v>
       </c>
     </row>
     <row r="508" spans="1:1">
       <c r="A508" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="510" spans="1:1">
       <c r="A510" s="2" t="s">
-        <v>363</v>
+        <v>328</v>
       </c>
     </row>
     <row r="511" spans="1:1">
       <c r="A511" s="2" t="s">
-        <v>767</v>
+        <v>732</v>
       </c>
     </row>
     <row r="513" spans="1:1">
       <c r="A513" s="2" t="s">
-        <v>364</v>
+        <v>329</v>
       </c>
     </row>
     <row r="514" spans="1:1">
       <c r="A514" s="2" t="s">
-        <v>360</v>
+        <v>325</v>
       </c>
     </row>
     <row r="515" spans="1:1">
       <c r="A515" s="2" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
     </row>
     <row r="516" spans="1:1">
       <c r="A516" s="2" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
     </row>
     <row r="518" spans="1:1">
       <c r="A518" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="519" spans="1:1">
       <c r="A519" s="2" t="s">
-        <v>706</v>
+        <v>671</v>
       </c>
     </row>
     <row r="520" spans="1:1">
       <c r="A520" s="2" t="s">
-        <v>707</v>
+        <v>672</v>
       </c>
     </row>
     <row r="521" spans="1:1">
       <c r="A521" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="522" spans="1:1">
       <c r="A522" s="2" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
     </row>
     <row r="523" spans="1:1">
       <c r="A523" s="2" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
     </row>
     <row r="524" spans="1:1">
       <c r="A524" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="526" spans="1:1">
       <c r="A526" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="527" spans="1:1">
       <c r="A527" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="528" spans="1:1">
       <c r="A528" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="529" spans="1:1">
       <c r="A529" s="2" t="s">
-        <v>710</v>
+        <v>675</v>
       </c>
     </row>
     <row r="530" spans="1:1">
       <c r="A530" s="2" t="s">
-        <v>711</v>
+        <v>676</v>
       </c>
     </row>
     <row r="531" spans="1:1">
       <c r="A531" s="2" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
     </row>
     <row r="532" spans="1:1">
       <c r="A532" s="2" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
     </row>
     <row r="534" spans="1:1">
       <c r="A534" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="535" spans="1:1">
       <c r="A535" s="2" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
     </row>
     <row r="536" spans="1:1">
       <c r="A536" s="2" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
     </row>
     <row r="537" spans="1:1">
       <c r="A537" s="2" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
     </row>
     <row r="538" spans="1:1">
       <c r="A538" s="2" t="s">
-        <v>718</v>
+        <v>683</v>
       </c>
     </row>
     <row r="540" spans="1:1">
       <c r="A540" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="541" spans="1:1">
       <c r="A541" s="2" t="s">
-        <v>719</v>
+        <v>684</v>
       </c>
     </row>
     <row r="542" spans="1:1">
       <c r="A542" s="2" t="s">
-        <v>763</v>
+        <v>728</v>
       </c>
     </row>
     <row r="543" spans="1:1">
       <c r="A543" s="2" t="s">
-        <v>764</v>
+        <v>729</v>
       </c>
     </row>
     <row r="544" spans="1:1">
       <c r="A544" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
     </row>
     <row r="545" spans="1:1">
       <c r="A545" s="2" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
     </row>
     <row r="546" spans="1:1">
       <c r="A546" s="2" t="s">
-        <v>757</v>
+        <v>722</v>
       </c>
     </row>
     <row r="548" spans="1:1">
       <c r="A548" s="2" t="s">
-        <v>720</v>
+        <v>685</v>
       </c>
     </row>
     <row r="549" spans="1:1">
       <c r="A549" s="2" t="s">
-        <v>721</v>
+        <v>686</v>
       </c>
     </row>
     <row r="551" spans="1:1">
       <c r="A551" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="553" spans="1:1">
       <c r="A553" s="2" t="s">
-        <v>363</v>
+        <v>328</v>
       </c>
     </row>
     <row r="554" spans="1:1">
       <c r="A554" s="2" t="s">
-        <v>767</v>
+        <v>732</v>
       </c>
     </row>
     <row r="556" spans="1:1">
       <c r="A556" s="2" t="s">
-        <v>364</v>
+        <v>329</v>
       </c>
     </row>
     <row r="557" spans="1:1">
       <c r="A557" s="2" t="s">
-        <v>360</v>
+        <v>325</v>
       </c>
     </row>
     <row r="558" spans="1:1">
       <c r="A558" s="2" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
     </row>
     <row r="559" spans="1:1">
       <c r="A559" s="2" t="s">
-        <v>660</v>
+        <v>625</v>
       </c>
     </row>
     <row r="560" spans="1:1">
       <c r="A560" s="2" t="s">
-        <v>704</v>
+        <v>669</v>
       </c>
     </row>
     <row r="561" spans="1:1">
       <c r="A561" s="2" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
     </row>
     <row r="563" spans="1:1">
       <c r="A563" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="564" spans="1:1">
       <c r="A564" s="2" t="s">
-        <v>706</v>
+        <v>671</v>
       </c>
     </row>
     <row r="565" spans="1:1">
       <c r="A565" s="2" t="s">
-        <v>707</v>
+        <v>672</v>
       </c>
     </row>
     <row r="566" spans="1:1">
       <c r="A566" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="567" spans="1:1">
       <c r="A567" s="2" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
     </row>
     <row r="568" spans="1:1">
       <c r="A568" s="2" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
     </row>
     <row r="569" spans="1:1">
       <c r="A569" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="571" spans="1:1">
       <c r="A571" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="572" spans="1:1">
       <c r="A572" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="573" spans="1:1">
       <c r="A573" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="574" spans="1:1">
       <c r="A574" s="2" t="s">
-        <v>710</v>
+        <v>675</v>
       </c>
     </row>
     <row r="575" spans="1:1">
       <c r="A575" s="2" t="s">
-        <v>711</v>
+        <v>676</v>
       </c>
     </row>
     <row r="576" spans="1:1">
       <c r="A576" s="2" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
     </row>
     <row r="577" spans="1:1">
       <c r="A577" s="2" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
     </row>
     <row r="579" spans="1:1">
       <c r="A579" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="580" spans="1:1">
       <c r="A580" s="2" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
     </row>
     <row r="581" spans="1:1">
       <c r="A581" s="2" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
     </row>
     <row r="582" spans="1:1">
       <c r="A582" s="2" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
     </row>
     <row r="583" spans="1:1">
       <c r="A583" s="2" t="s">
-        <v>718</v>
+        <v>683</v>
       </c>
     </row>
     <row r="585" spans="1:1">
       <c r="A585" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="586" spans="1:1">
       <c r="A586" s="2" t="s">
-        <v>719</v>
+        <v>684</v>
       </c>
     </row>
     <row r="587" spans="1:1">
       <c r="A587" s="2" t="s">
-        <v>763</v>
+        <v>728</v>
       </c>
     </row>
     <row r="588" spans="1:1">
       <c r="A588" s="2" t="s">
-        <v>764</v>
+        <v>729</v>
       </c>
     </row>
     <row r="589" spans="1:1">
       <c r="A589" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
     </row>
     <row r="590" spans="1:1">
       <c r="A590" s="2" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
     </row>
     <row r="591" spans="1:1">
       <c r="A591" s="2" t="s">
-        <v>757</v>
+        <v>722</v>
       </c>
     </row>
     <row r="593" spans="1:1">
       <c r="A593" s="2" t="s">
-        <v>720</v>
+        <v>685</v>
       </c>
     </row>
     <row r="594" spans="1:1">
       <c r="A594" s="2" t="s">
-        <v>721</v>
+        <v>686</v>
       </c>
     </row>
     <row r="596" spans="1:1">
       <c r="A596" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="598" spans="1:1">
       <c r="A598" s="2" t="s">
-        <v>363</v>
+        <v>328</v>
       </c>
     </row>
     <row r="599" spans="1:1">
       <c r="A599" s="2" t="s">
-        <v>767</v>
+        <v>732</v>
       </c>
     </row>
     <row r="601" spans="1:1">
       <c r="A601" s="2" t="s">
-        <v>364</v>
+        <v>329</v>
       </c>
     </row>
     <row r="602" spans="1:1">
       <c r="A602" s="2" t="s">
-        <v>660</v>
+        <v>625</v>
       </c>
     </row>
     <row r="603" spans="1:1">
       <c r="A603" s="2" t="s">
-        <v>704</v>
+        <v>669</v>
       </c>
     </row>
     <row r="604" spans="1:1">
       <c r="A604" s="2" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
     </row>
     <row r="606" spans="1:1">
       <c r="A606" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="607" spans="1:1">
       <c r="A607" s="2" t="s">
-        <v>706</v>
+        <v>671</v>
       </c>
     </row>
     <row r="608" spans="1:1">
       <c r="A608" s="2" t="s">
-        <v>707</v>
+        <v>672</v>
       </c>
     </row>
     <row r="609" spans="1:1">
       <c r="A609" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="610" spans="1:1">
       <c r="A610" s="2" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
     </row>
     <row r="611" spans="1:1">
       <c r="A611" s="2" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
     </row>
     <row r="612" spans="1:1">
       <c r="A612" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="614" spans="1:1">
       <c r="A614" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="615" spans="1:1">
       <c r="A615" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="616" spans="1:1">
       <c r="A616" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="617" spans="1:1">
       <c r="A617" s="2" t="s">
-        <v>710</v>
+        <v>675</v>
       </c>
     </row>
     <row r="618" spans="1:1">
       <c r="A618" s="2" t="s">
-        <v>711</v>
+        <v>676</v>
       </c>
     </row>
     <row r="619" spans="1:1">
       <c r="A619" s="2" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
     </row>
     <row r="620" spans="1:1">
       <c r="A620" s="2" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
     </row>
     <row r="622" spans="1:1">
       <c r="A622" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="623" spans="1:1">
       <c r="A623" s="2" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
     </row>
     <row r="624" spans="1:1">
       <c r="A624" s="2" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
     </row>
     <row r="625" spans="1:1">
       <c r="A625" s="2" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
     </row>
     <row r="626" spans="1:1">
       <c r="A626" s="2" t="s">
-        <v>718</v>
+        <v>683</v>
       </c>
     </row>
     <row r="628" spans="1:1">
       <c r="A628" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="629" spans="1:1">
       <c r="A629" s="2" t="s">
-        <v>719</v>
+        <v>684</v>
       </c>
     </row>
     <row r="630" spans="1:1">
       <c r="A630" s="2" t="s">
-        <v>763</v>
+        <v>728</v>
       </c>
     </row>
     <row r="631" spans="1:1">
       <c r="A631" s="2" t="s">
-        <v>764</v>
+        <v>729</v>
       </c>
     </row>
     <row r="632" spans="1:1">
       <c r="A632" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
     </row>
     <row r="633" spans="1:1">
       <c r="A633" s="2" t="s">
-        <v>766</v>
+        <v>731</v>
       </c>
     </row>
     <row r="634" spans="1:1">
       <c r="A634" s="2" t="s">
-        <v>757</v>
+        <v>722</v>
       </c>
     </row>
     <row r="636" spans="1:1">
       <c r="A636" s="2" t="s">
-        <v>720</v>
+        <v>685</v>
       </c>
     </row>
     <row r="637" spans="1:1">
       <c r="A637" s="2" t="s">
-        <v>721</v>
+        <v>686</v>
       </c>
     </row>
     <row r="639" spans="1:1">
       <c r="A639" s="2" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="641" spans="1:1">
       <c r="A641" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
     </row>
     <row r="642" spans="1:1">
       <c r="A642" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="644" spans="1:1">
       <c r="A644" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="645" spans="1:1">
       <c r="A645" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
     </row>
     <row r="646" spans="1:1">
       <c r="A646" s="2" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="648" spans="1:1">
       <c r="A648" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="649" spans="1:1">
       <c r="A649" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
     </row>
     <row r="650" spans="1:1">
       <c r="A650" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="652" spans="1:1">
       <c r="A652" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="653" spans="1:1">
       <c r="A653" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
     </row>
     <row r="654" spans="1:1">
       <c r="A654" s="2" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="656" spans="1:1">
       <c r="A656" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="657" spans="1:1">
       <c r="A657" s="2" t="s">
-        <v>772</v>
+        <v>737</v>
       </c>
     </row>
     <row r="658" spans="1:1">
       <c r="A658" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="659" spans="1:1">
       <c r="A659" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="660" spans="1:1">
       <c r="A660" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
     </row>
     <row r="661" spans="1:1">
       <c r="A661" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="663" spans="1:1">
       <c r="A663" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="664" spans="1:1">
       <c r="A664" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
     </row>
     <row r="665" spans="1:1">
       <c r="A665" s="2" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="667" spans="1:1">
       <c r="A667" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="668" spans="1:1">
       <c r="A668" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
     </row>
     <row r="669" spans="1:1">
       <c r="A669" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="671" spans="1:1">
       <c r="A671" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="672" spans="1:1">
       <c r="A672" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
     </row>
     <row r="673" spans="1:1">
       <c r="A673" s="2" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="674" spans="1:1">
       <c r="A674" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="676" spans="1:1">
       <c r="A676" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="677" spans="1:1">
       <c r="A677" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
     </row>
     <row r="678" spans="1:1">
       <c r="A678" s="2" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="680" spans="1:1">
       <c r="A680" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="681" spans="1:1">
       <c r="A681" s="2" t="s">
-        <v>773</v>
+        <v>738</v>
       </c>
     </row>
     <row r="682" spans="1:1">
       <c r="A682" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="683" spans="1:1">
       <c r="A683" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
     </row>
     <row r="684" spans="1:1">
       <c r="A684" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="686" spans="1:1">
       <c r="A686" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="687" spans="1:1">
       <c r="A687" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
     </row>
     <row r="688" spans="1:1">
       <c r="A688" s="2" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="690" spans="1:1">
       <c r="A690" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="691" spans="1:1">
       <c r="A691" s="2" t="s">
-        <v>774</v>
+        <v>739</v>
       </c>
     </row>
     <row r="692" spans="1:1">
       <c r="A692" s="2" t="s">
-        <v>775</v>
+        <v>740</v>
       </c>
     </row>
     <row r="693" spans="1:1">
       <c r="A693" s="2" t="s">
-        <v>776</v>
+        <v>741</v>
       </c>
     </row>
     <row r="695" spans="1:1">
       <c r="A695" s="2" t="s">
-        <v>777</v>
+        <v>742</v>
       </c>
     </row>
     <row r="697" spans="1:1">
       <c r="A697" s="2" t="s">
-        <v>646</v>
+        <v>611</v>
       </c>
     </row>
     <row r="698" spans="1:1">
       <c r="A698" s="2" t="s">
-        <v>647</v>
+        <v>612</v>
       </c>
     </row>
     <row r="699" spans="1:1">
       <c r="A699" s="2" t="s">
-        <v>648</v>
+        <v>613</v>
       </c>
     </row>
     <row r="700" spans="1:1">
       <c r="A700" s="2" t="s">
-        <v>778</v>
+        <v>743</v>
       </c>
     </row>
     <row r="701" spans="1:1">
       <c r="A701" s="2" t="s">
-        <v>651</v>
+        <v>616</v>
       </c>
     </row>
     <row r="702" spans="1:1">
       <c r="A702" s="2" t="s">
-        <v>652</v>
+        <v>617</v>
       </c>
     </row>
     <row r="704" spans="1:1">
       <c r="A704" s="2" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
     </row>
     <row r="705" spans="1:1">
       <c r="A705" s="2" t="s">
-        <v>779</v>
+        <v>744</v>
       </c>
     </row>
     <row r="706" spans="1:1">
       <c r="A706" s="2" t="s">
-        <v>780</v>
+        <v>745</v>
       </c>
     </row>
     <row r="707" spans="1:1">
       <c r="A707" s="2" t="s">
-        <v>658</v>
+        <v>623</v>
       </c>
     </row>
     <row r="708" spans="1:1">
       <c r="A708" s="2" t="s">
-        <v>781</v>
+        <v>746</v>
       </c>
     </row>
     <row r="709" spans="1:1">
       <c r="A709" s="2" t="s">
-        <v>782</v>
+        <v>747</v>
       </c>
     </row>
     <row r="711" spans="1:1">
       <c r="A711" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="712" spans="1:1">
       <c r="A712" s="2" t="s">
-        <v>664</v>
+        <v>629</v>
       </c>
     </row>
     <row r="713" spans="1:1">
       <c r="A713" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="714" spans="1:1">
       <c r="A714" s="2" t="s">
-        <v>666</v>
+        <v>631</v>
       </c>
     </row>
     <row r="715" spans="1:1">
       <c r="A715" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="717" spans="1:1">
       <c r="A717" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="718" spans="1:1">
       <c r="A718" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="719" spans="1:1">
       <c r="A719" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="720" spans="1:1">
       <c r="A720" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
     </row>
     <row r="721" spans="1:1">
       <c r="A721" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="723" spans="1:1">
       <c r="A723" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="724" spans="1:1">
       <c r="A724" s="2" t="s">
-        <v>664</v>
+        <v>629</v>
       </c>
     </row>
     <row r="725" spans="1:1">
       <c r="A725" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="726" spans="1:1">
       <c r="A726" s="2" t="s">
-        <v>666</v>
+        <v>631</v>
       </c>
     </row>
     <row r="727" spans="1:1">
       <c r="A727" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="729" spans="1:1">
       <c r="A729" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="730" spans="1:1">
       <c r="A730" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="731" spans="1:1">
       <c r="A731" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="732" spans="1:1">
       <c r="A732" s="2" t="s">
-        <v>768</v>
+        <v>733</v>
       </c>
     </row>
     <row r="733" spans="1:1">
       <c r="A733" s="2" t="s">
-        <v>769</v>
+        <v>734</v>
       </c>
     </row>
     <row r="735" spans="1:1">
       <c r="A735" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="736" spans="1:1">
       <c r="A736" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
     </row>
     <row r="737" spans="1:1">
       <c r="A737" s="2" t="s">
-        <v>783</v>
+        <v>748</v>
       </c>
     </row>
     <row r="738" spans="1:1">
       <c r="A738" s="2" t="s">
-        <v>784</v>
+        <v>749</v>
       </c>
     </row>
     <row r="739" spans="1:1">
       <c r="A739" s="2" t="s">
-        <v>597</v>
+        <v>562</v>
       </c>
     </row>
     <row r="740" spans="1:1">
       <c r="A740" s="2" t="s">
-        <v>578</v>
+        <v>543</v>
       </c>
     </row>
     <row r="741" spans="1:1">
       <c r="A741" s="2" t="s">
-        <v>785</v>
+        <v>750</v>
       </c>
     </row>
     <row r="742" spans="1:1">
       <c r="A742" s="2" t="s">
-        <v>786</v>
+        <v>751</v>
       </c>
     </row>
     <row r="743" spans="1:1">
       <c r="A743" s="2" t="s">
-        <v>600</v>
+        <v>565</v>
       </c>
     </row>
     <row r="745" spans="1:1">
       <c r="A745" s="2" t="s">
-        <v>601</v>
+        <v>566</v>
       </c>
     </row>
     <row r="747" spans="1:1">
       <c r="A747" s="2" t="s">
-        <v>787</v>
+        <v>752</v>
       </c>
     </row>
     <row r="748" spans="1:1">
       <c r="A748" s="2" t="s">
-        <v>788</v>
+        <v>753</v>
       </c>
     </row>
     <row r="749" spans="1:1">
       <c r="A749" s="2" t="s">
-        <v>789</v>
+        <v>754</v>
       </c>
     </row>
     <row r="750" spans="1:1">
       <c r="A750" s="2" t="s">
-        <v>790</v>
+        <v>755</v>
       </c>
     </row>
     <row r="751" spans="1:1">
       <c r="A751" s="2" t="s">
-        <v>791</v>
+        <v>756</v>
       </c>
     </row>
     <row r="752" spans="1:1">
       <c r="A752" s="2" t="s">
-        <v>792</v>
+        <v>757</v>
       </c>
     </row>
     <row r="753" spans="1:1">
       <c r="A753" s="2" t="s">
-        <v>793</v>
+        <v>758</v>
       </c>
     </row>
     <row r="754" spans="1:1">
       <c r="A754" s="2" t="s">
-        <v>794</v>
+        <v>759</v>
       </c>
     </row>
     <row r="755" spans="1:1">
       <c r="A755" s="2" t="s">
-        <v>795</v>
+        <v>760</v>
       </c>
     </row>
     <row r="756" spans="1:1">
       <c r="A756" s="2" t="s">
-        <v>796</v>
+        <v>761</v>
       </c>
     </row>
     <row r="757" spans="1:1">
       <c r="A757" s="2" t="s">
-        <v>797</v>
+        <v>762</v>
       </c>
     </row>
     <row r="758" spans="1:1">
       <c r="A758" s="2" t="s">
-        <v>798</v>
+        <v>763</v>
       </c>
     </row>
     <row r="759" spans="1:1">
       <c r="A759" s="2" t="s">
-        <v>799</v>
+        <v>764</v>
       </c>
     </row>
     <row r="760" spans="1:1">
       <c r="A760" s="2" t="s">
-        <v>800</v>
+        <v>765</v>
       </c>
     </row>
     <row r="761" spans="1:1">
       <c r="A761" s="2" t="s">
-        <v>801</v>
+        <v>766</v>
       </c>
     </row>
     <row r="762" spans="1:1">
       <c r="A762" s="2" t="s">
-        <v>802</v>
+        <v>767</v>
       </c>
     </row>
     <row r="763" spans="1:1">
       <c r="A763" s="2" t="s">
-        <v>803</v>
+        <v>768</v>
       </c>
     </row>
     <row r="764" spans="1:1">
       <c r="A764" s="2" t="s">
-        <v>804</v>
+        <v>769</v>
       </c>
     </row>
     <row r="765" spans="1:1">
       <c r="A765" s="2" t="s">
-        <v>805</v>
+        <v>770</v>
       </c>
     </row>
     <row r="766" spans="1:1">
       <c r="A766" s="2" t="s">
-        <v>806</v>
+        <v>771</v>
       </c>
     </row>
     <row r="767" spans="1:1">
       <c r="A767" s="2" t="s">
-        <v>620</v>
+        <v>585</v>
       </c>
     </row>
     <row r="768" spans="1:1">
       <c r="A768" s="2" t="s">
-        <v>807</v>
+        <v>772</v>
       </c>
     </row>
     <row r="769" spans="1:1">
       <c r="A769" s="2" t="s">
-        <v>808</v>
+        <v>773</v>
       </c>
     </row>
     <row r="770" spans="1:1">
       <c r="A770" s="2" t="s">
-        <v>809</v>
+        <v>774</v>
       </c>
     </row>
     <row r="771" spans="1:1">
       <c r="A771" s="2" t="s">
-        <v>810</v>
+        <v>775</v>
       </c>
     </row>
     <row r="772" spans="1:1">
       <c r="A772" s="2" t="s">
-        <v>811</v>
+        <v>776</v>
       </c>
     </row>
     <row r="773" spans="1:1">
       <c r="A773" s="2" t="s">
-        <v>812</v>
+        <v>777</v>
       </c>
     </row>
     <row r="774" spans="1:1">
       <c r="A774" s="2" t="s">
-        <v>813</v>
+        <v>778</v>
       </c>
     </row>
     <row r="775" spans="1:1">
       <c r="A775" s="2" t="s">
-        <v>814</v>
+        <v>779</v>
       </c>
     </row>
     <row r="776" spans="1:1">
       <c r="A776" s="2" t="s">
-        <v>815</v>
+        <v>780</v>
       </c>
     </row>
     <row r="777" spans="1:1">
       <c r="A777" s="2" t="s">
-        <v>816</v>
+        <v>781</v>
       </c>
     </row>
     <row r="778" spans="1:1">
       <c r="A778" s="2" t="s">
-        <v>817</v>
+        <v>782</v>
       </c>
     </row>
     <row r="779" spans="1:1">
       <c r="A779" s="2" t="s">
-        <v>818</v>
+        <v>783</v>
       </c>
     </row>
     <row r="780" spans="1:1">
       <c r="A780" s="2" t="s">
-        <v>819</v>
+        <v>784</v>
       </c>
     </row>
     <row r="781" spans="1:1">
       <c r="A781" s="2" t="s">
-        <v>820</v>
+        <v>785</v>
       </c>
     </row>
     <row r="782" spans="1:1">
       <c r="A782" s="2" t="s">
-        <v>821</v>
+        <v>786</v>
       </c>
     </row>
     <row r="783" spans="1:1">
       <c r="A783" s="2" t="s">
-        <v>822</v>
+        <v>787</v>
       </c>
     </row>
     <row r="784" spans="1:1">
       <c r="A784" s="2" t="s">
-        <v>823</v>
+        <v>788</v>
       </c>
     </row>
     <row r="786" spans="1:1">
       <c r="A786" s="2" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="787" spans="1:1">
       <c r="A787" s="2" t="s">
-        <v>637</v>
+        <v>602</v>
       </c>
     </row>
     <row r="789" spans="1:1">
       <c r="A789" s="2" t="s">
-        <v>824</v>
+        <v>789</v>
       </c>
     </row>
     <row r="790" spans="1:1">
       <c r="A790" s="2" t="s">
-        <v>825</v>
+        <v>790</v>
       </c>
     </row>
     <row r="792" spans="1:1">
       <c r="A792" s="2" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
     </row>
     <row r="793" spans="1:1">
       <c r="A793" s="2" t="s">
-        <v>826</v>
+        <v>791</v>
       </c>
     </row>
     <row r="794" spans="1:1">
       <c r="A794" s="2" t="s">
-        <v>827</v>
+        <v>792</v>
       </c>
     </row>
     <row r="795" spans="1:1">
       <c r="A795" s="2" t="s">
-        <v>828</v>
+        <v>793</v>
       </c>
     </row>
     <row r="797" spans="1:1">
       <c r="A797" s="2" t="s">
-        <v>644</v>
+        <v>609</v>
       </c>
     </row>
     <row r="798" spans="1:1">
       <c r="A798" s="2" t="s">
-        <v>829</v>
+        <v>794</v>
       </c>
     </row>
     <row r="799" spans="1:1">
       <c r="A799" s="2" t="s">
-        <v>830</v>
+        <v>795</v>
       </c>
     </row>
     <row r="800" spans="1:1">
       <c r="A800" s="2" t="s">
-        <v>646</v>
+        <v>611</v>
       </c>
     </row>
     <row r="801" spans="1:1">
       <c r="A801" s="2" t="s">
-        <v>647</v>
+        <v>612</v>
       </c>
     </row>
     <row r="802" spans="1:1">
       <c r="A802" s="2" t="s">
-        <v>648</v>
+        <v>613</v>
       </c>
     </row>
     <row r="803" spans="1:1">
       <c r="A803" s="2" t="s">
-        <v>831</v>
+        <v>796</v>
       </c>
     </row>
     <row r="804" spans="1:1">
       <c r="A804" s="2" t="s">
-        <v>832</v>
+        <v>797</v>
       </c>
     </row>
     <row r="805" spans="1:1">
       <c r="A805" s="2" t="s">
-        <v>651</v>
+        <v>616</v>
       </c>
     </row>
     <row r="806" spans="1:1">
       <c r="A806" s="2" t="s">
-        <v>652</v>
+        <v>617</v>
       </c>
     </row>
     <row r="808" spans="1:1">
       <c r="A808" s="2" t="s">
-        <v>653</v>
+        <v>618</v>
       </c>
     </row>
     <row r="809" spans="1:1">
       <c r="A809" s="2" t="s">
-        <v>833</v>
+        <v>798</v>
       </c>
     </row>
     <row r="810" spans="1:1">
       <c r="A810" s="2" t="s">
-        <v>834</v>
+        <v>799</v>
       </c>
     </row>
     <row r="811" spans="1:1">
       <c r="A811" s="2" t="s">
-        <v>835</v>
+        <v>800</v>
       </c>
     </row>
     <row r="812" spans="1:1">
       <c r="A812" s="2" t="s">
-        <v>836</v>
+        <v>801</v>
       </c>
     </row>
     <row r="813" spans="1:1">
       <c r="A813" s="2" t="s">
-        <v>658</v>
+        <v>623</v>
       </c>
     </row>
     <row r="814" spans="1:1">
       <c r="A814" s="2" t="s">
-        <v>659</v>
+        <v>624</v>
       </c>
     </row>
     <row r="815" spans="1:1">
       <c r="A815" s="2" t="s">
-        <v>660</v>
+        <v>625</v>
       </c>
     </row>
     <row r="816" spans="1:1">
       <c r="A816" s="2" t="s">
-        <v>704</v>
+        <v>669</v>
       </c>
     </row>
     <row r="817" spans="1:1">
       <c r="A817" s="2" t="s">
-        <v>705</v>
+        <v>670</v>
       </c>
     </row>
     <row r="819" spans="1:1">
       <c r="A819" s="2" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
     </row>
     <row r="820" spans="1:1">
       <c r="A820" s="2" t="s">
-        <v>837</v>
+        <v>802</v>
       </c>
     </row>
     <row r="821" spans="1:1">
       <c r="A821" s="2" t="s">
-        <v>838</v>
+        <v>803</v>
       </c>
     </row>
     <row r="822" spans="1:1">
       <c r="A822" s="2" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
     </row>
     <row r="823" spans="1:1">
       <c r="A823" s="2" t="s">
-        <v>708</v>
+        <v>673</v>
       </c>
     </row>
     <row r="824" spans="1:1">
       <c r="A824" s="2" t="s">
-        <v>709</v>
+        <v>674</v>
       </c>
     </row>
     <row r="825" spans="1:1">
       <c r="A825" s="2" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
     </row>
     <row r="827" spans="1:1">
       <c r="A827" s="2" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
     </row>
     <row r="828" spans="1:1">
       <c r="A828" s="2" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
     </row>
     <row r="829" spans="1:1">
       <c r="A829" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="830" spans="1:1">
       <c r="A830" s="2" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
     </row>
     <row r="831" spans="1:1">
       <c r="A831" s="2" t="s">
-        <v>839</v>
+        <v>804</v>
       </c>
     </row>
     <row r="832" spans="1:1">
       <c r="A832" s="2" t="s">
-        <v>840</v>
+        <v>805</v>
       </c>
     </row>
     <row r="833" spans="1:1">
       <c r="A833" s="2" t="s">
-        <v>712</v>
+        <v>677</v>
       </c>
     </row>
     <row r="834" spans="1:1">
       <c r="A834" s="2" t="s">
-        <v>713</v>
+        <v>678</v>
       </c>
     </row>
     <row r="836" spans="1:1">
       <c r="A836" s="2" t="s">
-        <v>714</v>
+        <v>679</v>
       </c>
     </row>
     <row r="837" spans="1:1">
       <c r="A837" s="2" t="s">
-        <v>715</v>
+        <v>680</v>
       </c>
     </row>
     <row r="838" spans="1:1">
       <c r="A838" s="2" t="s">
-        <v>716</v>
+        <v>681</v>
       </c>
     </row>
     <row r="839" spans="1:1">
       <c r="A839" s="2" t="s">
-        <v>717</v>
+        <v>682</v>
       </c>
     </row>
     <row r="840" spans="1:1">
       <c r="A840" s="2" t="s">
-        <v>718</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -14197,392 +14191,392 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>367</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>370</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>371</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="2" t="s">
-        <v>372</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="2" t="s">
-        <v>373</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="2" t="s">
-        <v>374</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="2" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>376</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>841</v>
+        <v>806</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>378</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="2" t="s">
-        <v>379</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="2" t="s">
-        <v>381</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="2" t="s">
-        <v>383</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>384</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>386</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="2" t="s">
-        <v>387</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>389</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>390</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>391</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>392</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="2" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>394</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>396</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="2" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>399</v>
+        <v>364</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>401</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>404</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>406</v>
+        <v>371</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="2" t="s">
-        <v>408</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>409</v>
+        <v>374</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="2" t="s">
-        <v>411</v>
+        <v>376</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="2" t="s">
-        <v>412</v>
+        <v>377</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>413</v>
+        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>414</v>
+        <v>379</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="2" t="s">
-        <v>415</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>416</v>
+        <v>381</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>417</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>418</v>
+        <v>383</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>419</v>
+        <v>384</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>420</v>
+        <v>385</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="2" t="s">
-        <v>421</v>
+        <v>386</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="2" t="s">
-        <v>422</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="2" t="s">
-        <v>423</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>424</v>
+        <v>389</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>425</v>
+        <v>390</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="2" t="s">
-        <v>426</v>
+        <v>391</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>427</v>
+        <v>392</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="2" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>433</v>
+        <v>398</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="2" t="s">
-        <v>434</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -14602,18 +14596,18 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>436</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="82.95" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90.55" customHeight="1">
@@ -14621,39 +14615,39 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="75.45" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>440</v>
+        <v>405</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>441</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="90.55" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>442</v>
+        <v>407</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>443</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="105.65" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>445</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="113.15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="42.45">
@@ -14661,7 +14655,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>876</v>
+        <v>828</v>
       </c>
     </row>
   </sheetData>
